--- a/sustainable_farm2025.xlsx
+++ b/sustainable_farm2025.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29316"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="653" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D135B0ED-115D-44CC-872C-7F1B626680F6}"/>
+  <xr:revisionPtr revIDLastSave="692" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{111A48F3-C43E-4C1B-86C1-B1CB438A1D1C}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="4" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall Farm" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="319">
   <si>
     <t>Calculation with 2 hectares scenarios</t>
   </si>
@@ -657,6 +657,297 @@
   </si>
   <si>
     <t>60ha detailed costs</t>
+  </si>
+  <si>
+    <t>Small Farm 1 ha</t>
+  </si>
+  <si>
+    <t>Medium Farm 5 ha</t>
+  </si>
+  <si>
+    <t>Large Farm 1 ha</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Calculation / Notes</t>
+  </si>
+  <si>
+    <t>Pump Load</t>
+  </si>
+  <si>
+    <t>1.5 kW</t>
+  </si>
+  <si>
+    <t>User-provided assumption</t>
+  </si>
+  <si>
+    <t>3.0 kW</t>
+  </si>
+  <si>
+    <t>7.5 kW</t>
+  </si>
+  <si>
+    <t>Pump Hours</t>
+  </si>
+  <si>
+    <t>4 h</t>
+  </si>
+  <si>
+    <t>6 h</t>
+  </si>
+  <si>
+    <t>8 h</t>
+  </si>
+  <si>
+    <t>Dryer Load</t>
+  </si>
+  <si>
+    <t>2.0 kW</t>
+  </si>
+  <si>
+    <t>4.0 kW</t>
+  </si>
+  <si>
+    <t>8.0 kW</t>
+  </si>
+  <si>
+    <t>Dryer Hours</t>
+  </si>
+  <si>
+    <t>Misc. Load</t>
+  </si>
+  <si>
+    <t>0.8 kW</t>
+  </si>
+  <si>
+    <t>Misc. Hours</t>
+  </si>
+  <si>
+    <t>3 h</t>
+  </si>
+  <si>
+    <t>Daily Energy</t>
+  </si>
+  <si>
+    <t>16.4 kWh/day</t>
+  </si>
+  <si>
+    <t>(1.5 kW * 4h) + (2.0 kW * 4h) + (0.8 kW * 3h)</t>
+  </si>
+  <si>
+    <t>48.0 kWh/day</t>
+  </si>
+  <si>
+    <t>(3.0 kW * 6h) + (4.0 kW * 6h) + (1.5 kW * 4h)</t>
+  </si>
+  <si>
+    <t>142.0 kWh/day</t>
+  </si>
+  <si>
+    <t>(7.5 kW * 8h) + (8.0 kW * 8h) + (3.0 kW * 6h)</t>
+  </si>
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>PSH</t>
+  </si>
+  <si>
+    <t>5.5 h</t>
+  </si>
+  <si>
+    <t>Tracker Gain</t>
+  </si>
+  <si>
+    <t>Effective PSH</t>
+  </si>
+  <si>
+    <t>6.6 h</t>
+  </si>
+  <si>
+    <t>5.5 h * (1 + 0.20)</t>
+  </si>
+  <si>
+    <t>System Derate</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>Required PV (kWp)</t>
+  </si>
+  <si>
+    <t>3.3 kWp</t>
+  </si>
+  <si>
+    <t>16.4 kWh / (6.6 h * 0.75)</t>
+  </si>
+  <si>
+    <t>9.7 kWp</t>
+  </si>
+  <si>
+    <t>48.0 kWh / (6.6 h * 0.75)</t>
+  </si>
+  <si>
+    <t>28.7 kWp</t>
+  </si>
+  <si>
+    <t>142.0 kWh / (6.6 h * 0.75)</t>
+  </si>
+  <si>
+    <t>Panel Wattage</t>
+  </si>
+  <si>
+    <t>400 W</t>
+  </si>
+  <si>
+    <t>Number of Panels</t>
+  </si>
+  <si>
+    <t>8 panels</t>
+  </si>
+  <si>
+    <t>(3.3 kWp * 1000) / 400 W</t>
+  </si>
+  <si>
+    <t>24 panels</t>
+  </si>
+  <si>
+    <t>(9.7 kWp * 1000) / 400 W</t>
+  </si>
+  <si>
+    <t>72 panels</t>
+  </si>
+  <si>
+    <t>(28.7 kWp * 1000) / 400 W</t>
+  </si>
+  <si>
+    <t>Inverter Efficiency</t>
+  </si>
+  <si>
+    <t>90% (0.90)</t>
+  </si>
+  <si>
+    <t>Battery DoD</t>
+  </si>
+  <si>
+    <t>80% (0.80)</t>
+  </si>
+  <si>
+    <t>Required Battery (usable)</t>
+  </si>
+  <si>
+    <t>23 kWh</t>
+  </si>
+  <si>
+    <t>16.4 kWh / (0.90 * 0.80)</t>
+  </si>
+  <si>
+    <t>67 kWh</t>
+  </si>
+  <si>
+    <t>48.0 kWh / (0.90 * 0.80)</t>
+  </si>
+  <si>
+    <t>197 kWh</t>
+  </si>
+  <si>
+    <t>142.0 kWh / (0.90 * 0.80)</t>
+  </si>
+  <si>
+    <t>Inverter Size</t>
+  </si>
+  <si>
+    <t>4.3 kW</t>
+  </si>
+  <si>
+    <t>Peak Load: 1.5 kW + 2.0 kW + 0.8 kW</t>
+  </si>
+  <si>
+    <t>8.5 kW</t>
+  </si>
+  <si>
+    <t>Peak Load: 3.0 kW + 4.0 kW + 1.5 kW</t>
+  </si>
+  <si>
+    <t>18.5 kW</t>
+  </si>
+  <si>
+    <t>Peak Load: 7.5 kW + 8.0 kW + 3.0 kW</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Daily Energy (kWh/day)</t>
+  </si>
+  <si>
+    <t>Required PV Array (kWp)</t>
+  </si>
+  <si>
+    <t>Number of 400 W Panels</t>
+  </si>
+  <si>
+    <t>Required Battery (usable kWh)</t>
+  </si>
+  <si>
+    <t>Inverter Size (kW, nominal)</t>
+  </si>
+  <si>
+    <t>Small farm (≈1 ha)</t>
+  </si>
+  <si>
+    <t>16.4</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>~8</t>
+  </si>
+  <si>
+    <t>~23</t>
+  </si>
+  <si>
+    <t>~4.3</t>
+  </si>
+  <si>
+    <t>Medium farm (≈5 ha)</t>
+  </si>
+  <si>
+    <t>48.0</t>
+  </si>
+  <si>
+    <t>9.7</t>
+  </si>
+  <si>
+    <t>~24</t>
+  </si>
+  <si>
+    <t>~67</t>
+  </si>
+  <si>
+    <t>~8.5</t>
+  </si>
+  <si>
+    <t>Large farm (≈20 ha)</t>
+  </si>
+  <si>
+    <t>142.0</t>
+  </si>
+  <si>
+    <t>28.7</t>
+  </si>
+  <si>
+    <t>~72</t>
+  </si>
+  <si>
+    <t>~197</t>
+  </si>
+  <si>
+    <t>~18.5</t>
   </si>
   <si>
     <t>Project: Security system design for a 2-hectare mango drying farm.</t>
@@ -714,7 +1005,7 @@
   <numFmts count="1">
     <numFmt numFmtId="6" formatCode="#,##0\ &quot;€&quot;;[Red]\-#,##0\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="43">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -995,6 +1286,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -1058,7 +1355,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -1431,11 +1728,63 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1544,16 +1893,49 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1617,39 +1999,28 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="9" fontId="42" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7061,102 +7432,102 @@
   </cols>
   <sheetData>
     <row r="4" spans="4:16" ht="18.75">
-      <c r="E4" s="93" t="s">
+      <c r="E4" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="94"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="94"/>
-      <c r="I4" s="94"/>
-      <c r="J4" s="94"/>
-      <c r="K4" s="94"/>
-      <c r="L4" s="94"/>
-      <c r="M4" s="94"/>
-      <c r="N4" s="94"/>
-      <c r="O4" s="94"/>
-      <c r="P4" s="95"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="77"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="75"/>
     </row>
     <row r="5" spans="4:16" ht="15.75">
-      <c r="E5" s="104" t="s">
+      <c r="E5" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="96" t="s">
+      <c r="F5" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="96" t="s">
+      <c r="G5" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="96" t="s">
+      <c r="H5" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="96" t="s">
+      <c r="I5" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="J5" s="96" t="s">
+      <c r="J5" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="96" t="s">
+      <c r="K5" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="L5" s="96" t="s">
+      <c r="L5" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="M5" s="96" t="s">
+      <c r="M5" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="96" t="s">
+      <c r="N5" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="O5" s="91" t="s">
+      <c r="O5" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="P5" s="92" t="s">
+      <c r="P5" s="67" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="4:16" ht="15.75">
-      <c r="E6" s="105" t="s">
+      <c r="E6" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="92">
+      <c r="F6" s="67">
         <v>2</v>
       </c>
-      <c r="G6" s="92">
+      <c r="G6" s="67">
         <f>F6*100</f>
         <v>200</v>
       </c>
-      <c r="H6" s="92">
+      <c r="H6" s="67">
         <f>(G6*100)/1000</f>
         <v>20</v>
       </c>
-      <c r="I6" s="92">
+      <c r="I6" s="67">
         <f>H6*7</f>
         <v>140</v>
       </c>
-      <c r="J6" s="92">
+      <c r="J6" s="67">
         <f>H6/5</f>
         <v>4</v>
       </c>
-      <c r="K6" s="92">
+      <c r="K6" s="67">
         <f>(H6*100)/(5*60)</f>
         <v>6.666666666666667</v>
       </c>
-      <c r="L6" s="92">
+      <c r="L6" s="67">
         <f>0.0027*J6*35</f>
         <v>0.378</v>
       </c>
-      <c r="M6" s="92">
+      <c r="M6" s="67">
         <f>L6*0.45</f>
         <v>0.1701</v>
       </c>
-      <c r="N6" s="92">
+      <c r="N6" s="67">
         <f>M6</f>
         <v>0.1701</v>
       </c>
-      <c r="O6" s="92">
+      <c r="O6" s="67">
         <v>0.84799999999999998</v>
       </c>
-      <c r="P6" s="96">
+      <c r="P6" s="68">
         <v>4</v>
       </c>
     </row>
@@ -7166,99 +7537,99 @@
     </row>
     <row r="10" spans="4:16" ht="18.75">
       <c r="D10" s="34"/>
-      <c r="E10" s="97" t="s">
+      <c r="E10" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="95"/>
+      <c r="F10" s="75"/>
       <c r="G10" s="31"/>
       <c r="H10" s="31"/>
-      <c r="I10" s="98" t="s">
+      <c r="I10" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="99"/>
-      <c r="K10" s="99"/>
-      <c r="L10" s="99"/>
-      <c r="M10" s="99"/>
-      <c r="N10" s="99"/>
-      <c r="O10" s="100"/>
+      <c r="J10" s="79"/>
+      <c r="K10" s="79"/>
+      <c r="L10" s="79"/>
+      <c r="M10" s="79"/>
+      <c r="N10" s="79"/>
+      <c r="O10" s="80"/>
     </row>
     <row r="11" spans="4:16" ht="18.75">
       <c r="D11" s="34"/>
-      <c r="E11" s="92" t="s">
+      <c r="E11" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="92" t="s">
+      <c r="F11" s="67" t="s">
         <v>17</v>
       </c>
       <c r="G11" s="34"/>
       <c r="H11" s="34"/>
-      <c r="I11" s="101" t="s">
+      <c r="I11" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="J11" s="96" t="s">
+      <c r="J11" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="K11" s="96" t="s">
+      <c r="K11" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="L11" s="96" t="s">
+      <c r="L11" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="M11" s="96" t="s">
+      <c r="M11" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="N11" s="96" t="s">
+      <c r="N11" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="O11" s="102" t="s">
+      <c r="O11" s="70" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="4:16" ht="18.75">
       <c r="D12" s="34"/>
-      <c r="E12" s="92" t="s">
+      <c r="E12" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="F12" s="92">
+      <c r="F12" s="67">
         <v>120</v>
       </c>
       <c r="G12" s="34"/>
       <c r="H12" s="34"/>
-      <c r="I12" s="92">
+      <c r="I12" s="67">
         <f>F14</f>
         <v>1400</v>
       </c>
-      <c r="J12" s="92">
+      <c r="J12" s="67">
         <f>0.35*2000</f>
         <v>700</v>
       </c>
-      <c r="K12" s="92">
+      <c r="K12" s="67">
         <f>P6*F12</f>
         <v>480</v>
       </c>
-      <c r="L12" s="92">
+      <c r="L12" s="67">
         <f>F13</f>
         <v>800</v>
       </c>
-      <c r="M12" s="92">
+      <c r="M12" s="67">
         <f>F16</f>
         <v>300</v>
       </c>
-      <c r="N12" s="92">
+      <c r="N12" s="67">
         <f>F17</f>
         <v>2500</v>
       </c>
-      <c r="O12" s="103">
+      <c r="O12" s="71">
         <f>I12+J12+K12+L12+M12+N12</f>
         <v>6180</v>
       </c>
     </row>
     <row r="13" spans="4:16" ht="15.75">
       <c r="D13" s="34"/>
-      <c r="E13" s="92" t="s">
+      <c r="E13" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="92">
+      <c r="F13" s="67">
         <v>800</v>
       </c>
       <c r="G13" s="34"/>
@@ -7266,10 +7637,10 @@
     </row>
     <row r="14" spans="4:16" ht="15.75">
       <c r="D14" s="34"/>
-      <c r="E14" s="92" t="s">
+      <c r="E14" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="92">
+      <c r="F14" s="67">
         <v>1400</v>
       </c>
       <c r="G14" s="34"/>
@@ -7278,30 +7649,30 @@
     </row>
     <row r="15" spans="4:16" ht="15.75">
       <c r="D15" s="34"/>
-      <c r="E15" s="92" t="s">
+      <c r="E15" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="92" t="s">
+      <c r="F15" s="67" t="s">
         <v>29</v>
       </c>
       <c r="G15" s="34"/>
       <c r="H15" s="34"/>
     </row>
     <row r="16" spans="4:16" ht="15.75">
-      <c r="E16" s="92" t="s">
+      <c r="E16" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="92">
+      <c r="F16" s="67">
         <v>300</v>
       </c>
       <c r="G16" s="34"/>
       <c r="H16" s="34"/>
     </row>
     <row r="17" spans="5:8" ht="15.75">
-      <c r="E17" s="92" t="s">
+      <c r="E17" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="92">
+      <c r="F17" s="67">
         <v>2500</v>
       </c>
       <c r="G17" s="34"/>
@@ -7342,17 +7713,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="24">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
     </row>
     <row r="3" spans="1:16" ht="19.5">
       <c r="A3" s="2" t="s">
@@ -7382,11 +7753,11 @@
       <c r="I3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K3" s="68" t="s">
+      <c r="K3" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="L3" s="69"/>
-      <c r="M3" s="64"/>
+      <c r="L3" s="84"/>
+      <c r="M3" s="65"/>
       <c r="N3" s="20" t="s">
         <v>43</v>
       </c>
@@ -7626,10 +7997,10 @@
       <c r="I9" s="1">
         <v>700000</v>
       </c>
-      <c r="K9" s="70" t="s">
+      <c r="K9" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="L9" s="71"/>
+      <c r="L9" s="86"/>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
       <c r="O9" s="8"/>
@@ -7698,12 +8069,12 @@
       <c r="I11" s="1">
         <v>535000</v>
       </c>
-      <c r="K11" s="72" t="s">
+      <c r="K11" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="73"/>
-      <c r="M11" s="73"/>
-      <c r="N11" s="73"/>
+      <c r="L11" s="88"/>
+      <c r="M11" s="88"/>
+      <c r="N11" s="88"/>
       <c r="O11" s="8"/>
       <c r="P11" s="62"/>
     </row>
@@ -7896,18 +8267,18 @@
       <c r="P16" s="62"/>
     </row>
     <row r="17" spans="1:9" ht="18.75">
-      <c r="A17" s="76" t="s">
+      <c r="A17" s="91" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="77"/>
-      <c r="C17" s="77"/>
-      <c r="D17" s="77"/>
-      <c r="F17" s="77" t="s">
+      <c r="B17" s="92"/>
+      <c r="C17" s="92"/>
+      <c r="D17" s="92"/>
+      <c r="F17" s="92" t="s">
         <v>78</v>
       </c>
-      <c r="G17" s="77"/>
-      <c r="H17" s="77"/>
-      <c r="I17" s="77"/>
+      <c r="G17" s="92"/>
+      <c r="H17" s="92"/>
+      <c r="I17" s="92"/>
     </row>
     <row r="18" spans="1:9" ht="36">
       <c r="A18" s="10" t="s">
@@ -8002,10 +8373,10 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="18.75">
-      <c r="A22" s="74" t="s">
+      <c r="A22" s="89" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="75"/>
+      <c r="B22" s="90"/>
       <c r="F22" s="12" t="s">
         <v>105</v>
       </c>
@@ -8131,34 +8502,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="59.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="94" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="79"/>
-      <c r="P1" s="79"/>
-      <c r="Q1" s="79"/>
-      <c r="R1" s="79"/>
-      <c r="S1" s="79"/>
-      <c r="T1" s="79"/>
-      <c r="U1" s="79"/>
-      <c r="V1" s="79"/>
-      <c r="W1" s="79"/>
-      <c r="X1" s="79"/>
-      <c r="Y1" s="79"/>
-      <c r="Z1" s="79"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="94"/>
+      <c r="N1" s="94"/>
+      <c r="O1" s="94"/>
+      <c r="P1" s="94"/>
+      <c r="Q1" s="94"/>
+      <c r="R1" s="94"/>
+      <c r="S1" s="94"/>
+      <c r="T1" s="94"/>
+      <c r="U1" s="94"/>
+      <c r="V1" s="94"/>
+      <c r="W1" s="94"/>
+      <c r="X1" s="94"/>
+      <c r="Y1" s="94"/>
+      <c r="Z1" s="94"/>
     </row>
     <row r="2" spans="1:26">
       <c r="A2" s="33"/>
@@ -8171,45 +8542,45 @@
       <c r="D4" s="34"/>
     </row>
     <row r="8" spans="1:26">
-      <c r="B8" s="80" t="s">
+      <c r="B8" s="95" t="s">
         <v>126</v>
       </c>
-      <c r="C8" s="80"/>
-      <c r="D8" s="81">
+      <c r="C8" s="95"/>
+      <c r="D8" s="96">
         <v>625</v>
       </c>
     </row>
     <row r="9" spans="1:26">
-      <c r="B9" s="80"/>
-      <c r="C9" s="80"/>
-      <c r="D9" s="82"/>
+      <c r="B9" s="95"/>
+      <c r="C9" s="95"/>
+      <c r="D9" s="97"/>
     </row>
     <row r="10" spans="1:26" ht="19.5">
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="98" t="s">
         <v>127</v>
       </c>
-      <c r="C10" s="84"/>
+      <c r="C10" s="99"/>
       <c r="D10" s="58">
         <v>1600</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="18.75">
-      <c r="B14" s="76" t="s">
+      <c r="B14" s="91" t="s">
         <v>128</v>
       </c>
-      <c r="C14" s="76"/>
-      <c r="D14" s="76"/>
-      <c r="O14" s="85" t="s">
+      <c r="C14" s="91"/>
+      <c r="D14" s="91"/>
+      <c r="O14" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="P14" s="85"/>
-      <c r="Q14" s="85"/>
-      <c r="R14" s="85"/>
-      <c r="S14" s="85"/>
-      <c r="T14" s="85"/>
-      <c r="U14" s="85"/>
-      <c r="V14" s="85"/>
-      <c r="W14" s="85"/>
+      <c r="P14" s="100"/>
+      <c r="Q14" s="100"/>
+      <c r="R14" s="100"/>
+      <c r="S14" s="100"/>
+      <c r="T14" s="100"/>
+      <c r="U14" s="100"/>
+      <c r="V14" s="100"/>
+      <c r="W14" s="100"/>
     </row>
     <row r="15" spans="1:26" ht="15.75">
       <c r="B15" s="46" t="s">
@@ -8221,11 +8592,11 @@
       <c r="D15" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="I15" s="86" t="s">
+      <c r="I15" s="101" t="s">
         <v>132</v>
       </c>
-      <c r="J15" s="86"/>
-      <c r="K15" s="86"/>
+      <c r="J15" s="101"/>
+      <c r="K15" s="101"/>
       <c r="O15" s="59" t="s">
         <v>133</v>
       </c>
@@ -8559,32 +8930,32 @@
       <c r="N31" s="35"/>
     </row>
     <row r="44" spans="3:26" ht="30">
-      <c r="C44" s="78" t="s">
+      <c r="C44" s="93" t="s">
         <v>178</v>
       </c>
-      <c r="D44" s="78"/>
-      <c r="E44" s="78"/>
-      <c r="F44" s="78"/>
-      <c r="G44" s="78"/>
-      <c r="H44" s="78"/>
-      <c r="I44" s="78"/>
-      <c r="J44" s="78"/>
-      <c r="K44" s="78"/>
-      <c r="L44" s="78"/>
-      <c r="M44" s="78"/>
-      <c r="N44" s="78"/>
-      <c r="O44" s="78"/>
-      <c r="P44" s="78"/>
-      <c r="Q44" s="78"/>
-      <c r="R44" s="78"/>
-      <c r="S44" s="78"/>
-      <c r="T44" s="78"/>
-      <c r="U44" s="78"/>
-      <c r="V44" s="78"/>
-      <c r="W44" s="78"/>
-      <c r="X44" s="78"/>
-      <c r="Y44" s="78"/>
-      <c r="Z44" s="78"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
+      <c r="F44" s="93"/>
+      <c r="G44" s="93"/>
+      <c r="H44" s="93"/>
+      <c r="I44" s="93"/>
+      <c r="J44" s="93"/>
+      <c r="K44" s="93"/>
+      <c r="L44" s="93"/>
+      <c r="M44" s="93"/>
+      <c r="N44" s="93"/>
+      <c r="O44" s="93"/>
+      <c r="P44" s="93"/>
+      <c r="Q44" s="93"/>
+      <c r="R44" s="93"/>
+      <c r="S44" s="93"/>
+      <c r="T44" s="93"/>
+      <c r="U44" s="93"/>
+      <c r="V44" s="93"/>
+      <c r="W44" s="93"/>
+      <c r="X44" s="93"/>
+      <c r="Y44" s="93"/>
+      <c r="Z44" s="93"/>
     </row>
     <row r="45" spans="3:26">
       <c r="C45" s="52" t="s">
@@ -9401,32 +9772,32 @@
       </c>
     </row>
     <row r="63" spans="3:26" ht="30">
-      <c r="C63" s="78" t="s">
+      <c r="C63" s="93" t="s">
         <v>203</v>
       </c>
-      <c r="D63" s="78"/>
-      <c r="E63" s="78"/>
-      <c r="F63" s="78"/>
-      <c r="G63" s="78"/>
-      <c r="H63" s="78"/>
-      <c r="I63" s="78"/>
-      <c r="J63" s="78"/>
-      <c r="K63" s="78"/>
-      <c r="L63" s="78"/>
-      <c r="M63" s="78"/>
-      <c r="N63" s="78"/>
-      <c r="O63" s="78"/>
-      <c r="P63" s="78"/>
-      <c r="Q63" s="78"/>
-      <c r="R63" s="78"/>
-      <c r="S63" s="78"/>
-      <c r="T63" s="78"/>
-      <c r="U63" s="78"/>
-      <c r="V63" s="78"/>
-      <c r="W63" s="78"/>
-      <c r="X63" s="78"/>
-      <c r="Y63" s="78"/>
-      <c r="Z63" s="78"/>
+      <c r="D63" s="93"/>
+      <c r="E63" s="93"/>
+      <c r="F63" s="93"/>
+      <c r="G63" s="93"/>
+      <c r="H63" s="93"/>
+      <c r="I63" s="93"/>
+      <c r="J63" s="93"/>
+      <c r="K63" s="93"/>
+      <c r="L63" s="93"/>
+      <c r="M63" s="93"/>
+      <c r="N63" s="93"/>
+      <c r="O63" s="93"/>
+      <c r="P63" s="93"/>
+      <c r="Q63" s="93"/>
+      <c r="R63" s="93"/>
+      <c r="S63" s="93"/>
+      <c r="T63" s="93"/>
+      <c r="U63" s="93"/>
+      <c r="V63" s="93"/>
+      <c r="W63" s="93"/>
+      <c r="X63" s="93"/>
+      <c r="Y63" s="93"/>
+      <c r="Z63" s="93"/>
     </row>
     <row r="64" spans="3:26">
       <c r="C64" s="52" t="s">
@@ -10243,32 +10614,32 @@
       </c>
     </row>
     <row r="81" spans="3:26" ht="30">
-      <c r="C81" s="78" t="s">
+      <c r="C81" s="93" t="s">
         <v>204</v>
       </c>
-      <c r="D81" s="78"/>
-      <c r="E81" s="78"/>
-      <c r="F81" s="78"/>
-      <c r="G81" s="78"/>
-      <c r="H81" s="78"/>
-      <c r="I81" s="78"/>
-      <c r="J81" s="78"/>
-      <c r="K81" s="78"/>
-      <c r="L81" s="78"/>
-      <c r="M81" s="78"/>
-      <c r="N81" s="78"/>
-      <c r="O81" s="78"/>
-      <c r="P81" s="78"/>
-      <c r="Q81" s="78"/>
-      <c r="R81" s="78"/>
-      <c r="S81" s="78"/>
-      <c r="T81" s="78"/>
-      <c r="U81" s="78"/>
-      <c r="V81" s="78"/>
-      <c r="W81" s="78"/>
-      <c r="X81" s="78"/>
-      <c r="Y81" s="78"/>
-      <c r="Z81" s="78"/>
+      <c r="D81" s="93"/>
+      <c r="E81" s="93"/>
+      <c r="F81" s="93"/>
+      <c r="G81" s="93"/>
+      <c r="H81" s="93"/>
+      <c r="I81" s="93"/>
+      <c r="J81" s="93"/>
+      <c r="K81" s="93"/>
+      <c r="L81" s="93"/>
+      <c r="M81" s="93"/>
+      <c r="N81" s="93"/>
+      <c r="O81" s="93"/>
+      <c r="P81" s="93"/>
+      <c r="Q81" s="93"/>
+      <c r="R81" s="93"/>
+      <c r="S81" s="93"/>
+      <c r="T81" s="93"/>
+      <c r="U81" s="93"/>
+      <c r="V81" s="93"/>
+      <c r="W81" s="93"/>
+      <c r="X81" s="93"/>
+      <c r="Y81" s="93"/>
+      <c r="Z81" s="93"/>
     </row>
     <row r="82" spans="3:26">
       <c r="C82" s="55" t="s">
@@ -11085,32 +11456,32 @@
       </c>
     </row>
     <row r="103" spans="3:26" ht="30">
-      <c r="C103" s="78" t="s">
+      <c r="C103" s="93" t="s">
         <v>205</v>
       </c>
-      <c r="D103" s="78"/>
-      <c r="E103" s="78"/>
-      <c r="F103" s="78"/>
-      <c r="G103" s="78"/>
-      <c r="H103" s="78"/>
-      <c r="I103" s="78"/>
-      <c r="J103" s="78"/>
-      <c r="K103" s="78"/>
-      <c r="L103" s="78"/>
-      <c r="M103" s="78"/>
-      <c r="N103" s="78"/>
-      <c r="O103" s="78"/>
-      <c r="P103" s="78"/>
-      <c r="Q103" s="78"/>
-      <c r="R103" s="78"/>
-      <c r="S103" s="78"/>
-      <c r="T103" s="78"/>
-      <c r="U103" s="78"/>
-      <c r="V103" s="78"/>
-      <c r="W103" s="78"/>
-      <c r="X103" s="78"/>
-      <c r="Y103" s="78"/>
-      <c r="Z103" s="78"/>
+      <c r="D103" s="93"/>
+      <c r="E103" s="93"/>
+      <c r="F103" s="93"/>
+      <c r="G103" s="93"/>
+      <c r="H103" s="93"/>
+      <c r="I103" s="93"/>
+      <c r="J103" s="93"/>
+      <c r="K103" s="93"/>
+      <c r="L103" s="93"/>
+      <c r="M103" s="93"/>
+      <c r="N103" s="93"/>
+      <c r="O103" s="93"/>
+      <c r="P103" s="93"/>
+      <c r="Q103" s="93"/>
+      <c r="R103" s="93"/>
+      <c r="S103" s="93"/>
+      <c r="T103" s="93"/>
+      <c r="U103" s="93"/>
+      <c r="V103" s="93"/>
+      <c r="W103" s="93"/>
+      <c r="X103" s="93"/>
+      <c r="Y103" s="93"/>
+      <c r="Z103" s="93"/>
     </row>
     <row r="104" spans="3:26">
       <c r="C104" s="55" t="s">
@@ -11954,18 +12325,768 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4665F9DD-CC96-4F39-ACC3-FD9DE8D7D975}">
-  <dimension ref="A1"/>
+  <dimension ref="B1:L24"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="40.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" customWidth="1"/>
+    <col min="8" max="8" width="39" customWidth="1"/>
+    <col min="10" max="10" width="20.42578125" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" customWidth="1"/>
+    <col min="12" max="12" width="41" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12">
+      <c r="C1" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="G1" s="62" t="s">
+        <v>207</v>
+      </c>
+      <c r="K1" s="62" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12">
+      <c r="B3" s="106" t="s">
+        <v>209</v>
+      </c>
+      <c r="C3" s="107" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" s="107" t="s">
+        <v>210</v>
+      </c>
+      <c r="F3" s="106" t="s">
+        <v>209</v>
+      </c>
+      <c r="G3" s="107" t="s">
+        <v>130</v>
+      </c>
+      <c r="H3" s="107" t="s">
+        <v>210</v>
+      </c>
+      <c r="J3" s="106" t="s">
+        <v>209</v>
+      </c>
+      <c r="K3" s="107" t="s">
+        <v>130</v>
+      </c>
+      <c r="L3" s="107" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="23.25">
+      <c r="B4" s="108" t="s">
+        <v>211</v>
+      </c>
+      <c r="C4" s="109" t="s">
+        <v>212</v>
+      </c>
+      <c r="D4" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="F4" s="108" t="s">
+        <v>211</v>
+      </c>
+      <c r="G4" s="109" t="s">
+        <v>214</v>
+      </c>
+      <c r="H4" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="J4" s="108" t="s">
+        <v>211</v>
+      </c>
+      <c r="K4" s="109" t="s">
+        <v>215</v>
+      </c>
+      <c r="L4" s="109" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="23.25">
+      <c r="B5" s="108" t="s">
+        <v>216</v>
+      </c>
+      <c r="C5" s="109" t="s">
+        <v>217</v>
+      </c>
+      <c r="D5" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="F5" s="108" t="s">
+        <v>216</v>
+      </c>
+      <c r="G5" s="109" t="s">
+        <v>218</v>
+      </c>
+      <c r="H5" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="J5" s="108" t="s">
+        <v>216</v>
+      </c>
+      <c r="K5" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="L5" s="109" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="23.25">
+      <c r="B6" s="108" t="s">
+        <v>220</v>
+      </c>
+      <c r="C6" s="109" t="s">
+        <v>221</v>
+      </c>
+      <c r="D6" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="F6" s="108" t="s">
+        <v>220</v>
+      </c>
+      <c r="G6" s="109" t="s">
+        <v>222</v>
+      </c>
+      <c r="H6" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="J6" s="108" t="s">
+        <v>220</v>
+      </c>
+      <c r="K6" s="109" t="s">
+        <v>223</v>
+      </c>
+      <c r="L6" s="109" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="23.25">
+      <c r="B7" s="108" t="s">
+        <v>224</v>
+      </c>
+      <c r="C7" s="109" t="s">
+        <v>217</v>
+      </c>
+      <c r="D7" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="F7" s="108" t="s">
+        <v>224</v>
+      </c>
+      <c r="G7" s="109" t="s">
+        <v>218</v>
+      </c>
+      <c r="H7" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="J7" s="108" t="s">
+        <v>224</v>
+      </c>
+      <c r="K7" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="L7" s="109" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="23.25">
+      <c r="B8" s="108" t="s">
+        <v>225</v>
+      </c>
+      <c r="C8" s="109" t="s">
+        <v>226</v>
+      </c>
+      <c r="D8" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="F8" s="108" t="s">
+        <v>225</v>
+      </c>
+      <c r="G8" s="109" t="s">
+        <v>212</v>
+      </c>
+      <c r="H8" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="J8" s="108" t="s">
+        <v>225</v>
+      </c>
+      <c r="K8" s="109" t="s">
+        <v>214</v>
+      </c>
+      <c r="L8" s="109" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="23.25">
+      <c r="B9" s="108" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9" s="109" t="s">
+        <v>228</v>
+      </c>
+      <c r="D9" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="F9" s="108" t="s">
+        <v>227</v>
+      </c>
+      <c r="G9" s="109" t="s">
+        <v>217</v>
+      </c>
+      <c r="H9" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="J9" s="108" t="s">
+        <v>227</v>
+      </c>
+      <c r="K9" s="109" t="s">
+        <v>218</v>
+      </c>
+      <c r="L9" s="109" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="23.25">
+      <c r="B10" s="108" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" s="109" t="s">
+        <v>230</v>
+      </c>
+      <c r="D10" s="109" t="s">
+        <v>231</v>
+      </c>
+      <c r="F10" s="108" t="s">
+        <v>229</v>
+      </c>
+      <c r="G10" s="109" t="s">
+        <v>232</v>
+      </c>
+      <c r="H10" s="109" t="s">
+        <v>233</v>
+      </c>
+      <c r="J10" s="108" t="s">
+        <v>229</v>
+      </c>
+      <c r="K10" s="109" t="s">
+        <v>234</v>
+      </c>
+      <c r="L10" s="109" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12">
+      <c r="B11" s="110" t="s">
+        <v>236</v>
+      </c>
+      <c r="C11" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="D11" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="F11" s="110" t="s">
+        <v>236</v>
+      </c>
+      <c r="G11" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="H11" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="J11" s="110" t="s">
+        <v>236</v>
+      </c>
+      <c r="K11" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="L11" s="111" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12">
+      <c r="B12" s="108" t="s">
+        <v>237</v>
+      </c>
+      <c r="C12" s="109" t="s">
+        <v>238</v>
+      </c>
+      <c r="D12" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="F12" s="108" t="s">
+        <v>237</v>
+      </c>
+      <c r="G12" s="109" t="s">
+        <v>238</v>
+      </c>
+      <c r="H12" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="J12" s="108" t="s">
+        <v>237</v>
+      </c>
+      <c r="K12" s="109" t="s">
+        <v>238</v>
+      </c>
+      <c r="L12" s="109" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="23.25">
+      <c r="B13" s="108" t="s">
+        <v>239</v>
+      </c>
+      <c r="C13" s="112">
+        <v>0.2</v>
+      </c>
+      <c r="D13" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="F13" s="108" t="s">
+        <v>239</v>
+      </c>
+      <c r="G13" s="112">
+        <v>0.2</v>
+      </c>
+      <c r="H13" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="J13" s="108" t="s">
+        <v>239</v>
+      </c>
+      <c r="K13" s="112">
+        <v>0.2</v>
+      </c>
+      <c r="L13" s="109" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="23.25">
+      <c r="B14" s="108" t="s">
+        <v>240</v>
+      </c>
+      <c r="C14" s="109" t="s">
+        <v>241</v>
+      </c>
+      <c r="D14" s="109" t="s">
+        <v>242</v>
+      </c>
+      <c r="F14" s="108" t="s">
+        <v>240</v>
+      </c>
+      <c r="G14" s="109" t="s">
+        <v>241</v>
+      </c>
+      <c r="H14" s="109" t="s">
+        <v>242</v>
+      </c>
+      <c r="J14" s="108" t="s">
+        <v>240</v>
+      </c>
+      <c r="K14" s="109" t="s">
+        <v>241</v>
+      </c>
+      <c r="L14" s="109" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="23.25">
+      <c r="B15" s="108" t="s">
+        <v>243</v>
+      </c>
+      <c r="C15" s="109" t="s">
+        <v>244</v>
+      </c>
+      <c r="D15" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="F15" s="108" t="s">
+        <v>243</v>
+      </c>
+      <c r="G15" s="109" t="s">
+        <v>244</v>
+      </c>
+      <c r="H15" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="J15" s="108" t="s">
+        <v>243</v>
+      </c>
+      <c r="K15" s="109" t="s">
+        <v>244</v>
+      </c>
+      <c r="L15" s="109" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="23.25">
+      <c r="B16" s="108" t="s">
+        <v>245</v>
+      </c>
+      <c r="C16" s="109" t="s">
+        <v>246</v>
+      </c>
+      <c r="D16" s="109" t="s">
+        <v>247</v>
+      </c>
+      <c r="F16" s="108" t="s">
+        <v>245</v>
+      </c>
+      <c r="G16" s="109" t="s">
+        <v>248</v>
+      </c>
+      <c r="H16" s="109" t="s">
+        <v>249</v>
+      </c>
+      <c r="J16" s="108" t="s">
+        <v>245</v>
+      </c>
+      <c r="K16" s="109" t="s">
+        <v>250</v>
+      </c>
+      <c r="L16" s="109" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="23.25">
+      <c r="B17" s="108" t="s">
+        <v>252</v>
+      </c>
+      <c r="C17" s="109" t="s">
+        <v>253</v>
+      </c>
+      <c r="D17" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="F17" s="108" t="s">
+        <v>252</v>
+      </c>
+      <c r="G17" s="109" t="s">
+        <v>253</v>
+      </c>
+      <c r="H17" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="J17" s="108" t="s">
+        <v>252</v>
+      </c>
+      <c r="K17" s="109" t="s">
+        <v>253</v>
+      </c>
+      <c r="L17" s="109" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="23.25">
+      <c r="B18" s="108" t="s">
+        <v>254</v>
+      </c>
+      <c r="C18" s="109" t="s">
+        <v>255</v>
+      </c>
+      <c r="D18" s="109" t="s">
+        <v>256</v>
+      </c>
+      <c r="F18" s="108" t="s">
+        <v>254</v>
+      </c>
+      <c r="G18" s="109" t="s">
+        <v>257</v>
+      </c>
+      <c r="H18" s="109" t="s">
+        <v>258</v>
+      </c>
+      <c r="J18" s="108" t="s">
+        <v>254</v>
+      </c>
+      <c r="K18" s="109" t="s">
+        <v>259</v>
+      </c>
+      <c r="L18" s="109" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12">
+      <c r="B19" s="110" t="s">
+        <v>236</v>
+      </c>
+      <c r="C19" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="D19" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="F19" s="110" t="s">
+        <v>236</v>
+      </c>
+      <c r="G19" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="H19" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="J19" s="110" t="s">
+        <v>236</v>
+      </c>
+      <c r="K19" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="L19" s="111" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="23.25">
+      <c r="B20" s="108" t="s">
+        <v>261</v>
+      </c>
+      <c r="C20" s="109" t="s">
+        <v>262</v>
+      </c>
+      <c r="D20" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="F20" s="108" t="s">
+        <v>261</v>
+      </c>
+      <c r="G20" s="109" t="s">
+        <v>262</v>
+      </c>
+      <c r="H20" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="J20" s="108" t="s">
+        <v>261</v>
+      </c>
+      <c r="K20" s="109" t="s">
+        <v>262</v>
+      </c>
+      <c r="L20" s="109" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="23.25">
+      <c r="B21" s="108" t="s">
+        <v>263</v>
+      </c>
+      <c r="C21" s="109" t="s">
+        <v>264</v>
+      </c>
+      <c r="D21" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="F21" s="108" t="s">
+        <v>263</v>
+      </c>
+      <c r="G21" s="109" t="s">
+        <v>264</v>
+      </c>
+      <c r="H21" s="109" t="s">
+        <v>213</v>
+      </c>
+      <c r="J21" s="108" t="s">
+        <v>263</v>
+      </c>
+      <c r="K21" s="109" t="s">
+        <v>264</v>
+      </c>
+      <c r="L21" s="109" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="35.25">
+      <c r="B22" s="108" t="s">
+        <v>265</v>
+      </c>
+      <c r="C22" s="109" t="s">
+        <v>266</v>
+      </c>
+      <c r="D22" s="109" t="s">
+        <v>267</v>
+      </c>
+      <c r="F22" s="108" t="s">
+        <v>265</v>
+      </c>
+      <c r="G22" s="109" t="s">
+        <v>268</v>
+      </c>
+      <c r="H22" s="109" t="s">
+        <v>269</v>
+      </c>
+      <c r="J22" s="108" t="s">
+        <v>265</v>
+      </c>
+      <c r="K22" s="109" t="s">
+        <v>270</v>
+      </c>
+      <c r="L22" s="109" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12">
+      <c r="B23" s="110" t="s">
+        <v>236</v>
+      </c>
+      <c r="C23" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="D23" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="F23" s="110" t="s">
+        <v>236</v>
+      </c>
+      <c r="G23" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="H23" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="J23" s="110" t="s">
+        <v>236</v>
+      </c>
+      <c r="K23" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="L23" s="111" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="23.25">
+      <c r="B24" s="108" t="s">
+        <v>272</v>
+      </c>
+      <c r="C24" s="109" t="s">
+        <v>273</v>
+      </c>
+      <c r="D24" s="109" t="s">
+        <v>274</v>
+      </c>
+      <c r="F24" s="108" t="s">
+        <v>272</v>
+      </c>
+      <c r="G24" s="109" t="s">
+        <v>275</v>
+      </c>
+      <c r="H24" s="109" t="s">
+        <v>276</v>
+      </c>
+      <c r="J24" s="108" t="s">
+        <v>272</v>
+      </c>
+      <c r="K24" s="109" t="s">
+        <v>277</v>
+      </c>
+      <c r="L24" s="109" t="s">
+        <v>278</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549D1EB9-DCF8-4E0D-A2D2-EFBE00CED3CD}">
-  <dimension ref="A1"/>
+  <dimension ref="B4:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="21.28515625" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" customWidth="1"/>
+    <col min="5" max="5" width="26.42578125" customWidth="1"/>
+    <col min="6" max="6" width="31" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:7" ht="23.25">
+      <c r="B4" s="106" t="s">
+        <v>279</v>
+      </c>
+      <c r="C4" s="107" t="s">
+        <v>280</v>
+      </c>
+      <c r="D4" s="107" t="s">
+        <v>281</v>
+      </c>
+      <c r="E4" s="107" t="s">
+        <v>282</v>
+      </c>
+      <c r="F4" s="107" t="s">
+        <v>283</v>
+      </c>
+      <c r="G4" s="113" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="35.25">
+      <c r="B5" s="108" t="s">
+        <v>285</v>
+      </c>
+      <c r="C5" s="109" t="s">
+        <v>286</v>
+      </c>
+      <c r="D5" s="109" t="s">
+        <v>287</v>
+      </c>
+      <c r="E5" s="109" t="s">
+        <v>288</v>
+      </c>
+      <c r="F5" s="109" t="s">
+        <v>289</v>
+      </c>
+      <c r="G5" s="109" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="35.25">
+      <c r="B6" s="108" t="s">
+        <v>291</v>
+      </c>
+      <c r="C6" s="109" t="s">
+        <v>292</v>
+      </c>
+      <c r="D6" s="109" t="s">
+        <v>293</v>
+      </c>
+      <c r="E6" s="109" t="s">
+        <v>294</v>
+      </c>
+      <c r="F6" s="109" t="s">
+        <v>295</v>
+      </c>
+      <c r="G6" s="109" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="35.25">
+      <c r="B7" s="108" t="s">
+        <v>297</v>
+      </c>
+      <c r="C7" s="109" t="s">
+        <v>298</v>
+      </c>
+      <c r="D7" s="109" t="s">
+        <v>299</v>
+      </c>
+      <c r="E7" s="109" t="s">
+        <v>300</v>
+      </c>
+      <c r="F7" s="109" t="s">
+        <v>301</v>
+      </c>
+      <c r="G7" s="109" t="s">
+        <v>302</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11996,63 +13117,63 @@
       <c r="F5" s="22"/>
     </row>
     <row r="6" spans="3:6">
-      <c r="C6" s="87" t="s">
-        <v>206</v>
-      </c>
-      <c r="D6" s="87"/>
-      <c r="E6" s="87"/>
-      <c r="F6" s="87"/>
+      <c r="C6" s="102" t="s">
+        <v>303</v>
+      </c>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
     </row>
     <row r="7" spans="3:6">
-      <c r="C7" s="87" t="s">
-        <v>207</v>
-      </c>
-      <c r="D7" s="87"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="87"/>
+      <c r="C7" s="102" t="s">
+        <v>304</v>
+      </c>
+      <c r="D7" s="102"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
     </row>
     <row r="8" spans="3:6">
-      <c r="C8" s="88" t="s">
-        <v>208</v>
-      </c>
-      <c r="D8" s="88"/>
-      <c r="E8" s="88"/>
-      <c r="F8" s="88"/>
+      <c r="C8" s="103" t="s">
+        <v>305</v>
+      </c>
+      <c r="D8" s="103"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="103"/>
     </row>
     <row r="9" spans="3:6">
-      <c r="C9" s="89" t="s">
-        <v>208</v>
-      </c>
-      <c r="D9" s="90"/>
-      <c r="E9" s="90"/>
-      <c r="F9" s="90"/>
+      <c r="C9" s="104" t="s">
+        <v>305</v>
+      </c>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
     </row>
     <row r="10" spans="3:6">
-      <c r="C10" s="65"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
     </row>
     <row r="11" spans="3:6" ht="15.75">
       <c r="C11" s="23" t="s">
-        <v>209</v>
+        <v>306</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>210</v>
+        <v>307</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>211</v>
+        <v>308</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>212</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" spans="3:6" ht="15.75">
       <c r="C12" s="24" t="s">
-        <v>213</v>
+        <v>310</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>214</v>
+        <v>311</v>
       </c>
       <c r="E12" s="26">
         <v>9</v>
@@ -12063,7 +13184,7 @@
     </row>
     <row r="13" spans="3:6" ht="15.75">
       <c r="C13" s="27" t="s">
-        <v>215</v>
+        <v>312</v>
       </c>
       <c r="D13" s="27">
         <v>12</v>
@@ -12077,7 +13198,7 @@
     </row>
     <row r="14" spans="3:6" ht="15.75">
       <c r="C14" s="25" t="s">
-        <v>216</v>
+        <v>313</v>
       </c>
       <c r="D14" s="25">
         <v>2</v>
@@ -12091,7 +13212,7 @@
     </row>
     <row r="15" spans="3:6" ht="15.75">
       <c r="C15" s="27" t="s">
-        <v>217</v>
+        <v>314</v>
       </c>
       <c r="D15" s="27">
         <v>8</v>
@@ -12105,7 +13226,7 @@
     </row>
     <row r="16" spans="3:6" ht="15.75">
       <c r="C16" s="25" t="s">
-        <v>218</v>
+        <v>315</v>
       </c>
       <c r="D16" s="25">
         <v>2</v>
@@ -12119,7 +13240,7 @@
     </row>
     <row r="17" spans="3:6" ht="15.75">
       <c r="C17" s="27" t="s">
-        <v>219</v>
+        <v>316</v>
       </c>
       <c r="D17" s="27">
         <v>1</v>
@@ -12133,13 +13254,13 @@
     </row>
     <row r="18" spans="3:6" ht="15.75">
       <c r="C18" s="24" t="s">
-        <v>220</v>
+        <v>317</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>221</v>
+        <v>318</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>221</v>
+        <v>318</v>
       </c>
       <c r="F18" s="30">
         <v>10700</v>

--- a/sustainable_farm2025.xlsx
+++ b/sustainable_farm2025.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29316"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29311"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="692" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{111A48F3-C43E-4C1B-86C1-B1CB438A1D1C}"/>
+  <xr:revisionPtr revIDLastSave="756" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5610DEF3-0F55-4873-A6C5-1CA2434DB8BF}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overall Farm" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="259">
   <si>
     <t>Calculation with 2 hectares scenarios</t>
   </si>
@@ -659,13 +659,7 @@
     <t>60ha detailed costs</t>
   </si>
   <si>
-    <t>Small Farm 1 ha</t>
-  </si>
-  <si>
-    <t>Medium Farm 5 ha</t>
-  </si>
-  <si>
-    <t>Large Farm 1 ha</t>
+    <t>Small Farm 2 ha</t>
   </si>
   <si>
     <t>Metric</t>
@@ -677,207 +671,84 @@
     <t>Pump Load</t>
   </si>
   <si>
-    <t>1.5 kW</t>
+    <t>kw</t>
+  </si>
+  <si>
+    <t>Pump Hours</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>Dryer Load</t>
+  </si>
+  <si>
+    <t>Dryer Hours</t>
+  </si>
+  <si>
+    <t>Misc. Load</t>
+  </si>
+  <si>
+    <t>Misc. Hours</t>
+  </si>
+  <si>
+    <t>Daily Energy</t>
+  </si>
+  <si>
+    <t>kwh</t>
+  </si>
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>PSH</t>
+  </si>
+  <si>
+    <t>Tracker Gain</t>
   </si>
   <si>
     <t>User-provided assumption</t>
   </si>
   <si>
-    <t>3.0 kW</t>
-  </si>
-  <si>
-    <t>7.5 kW</t>
-  </si>
-  <si>
-    <t>Pump Hours</t>
-  </si>
-  <si>
-    <t>4 h</t>
-  </si>
-  <si>
-    <t>6 h</t>
-  </si>
-  <si>
-    <t>8 h</t>
-  </si>
-  <si>
-    <t>Dryer Load</t>
-  </si>
-  <si>
-    <t>2.0 kW</t>
-  </si>
-  <si>
-    <t>4.0 kW</t>
-  </si>
-  <si>
-    <t>8.0 kW</t>
-  </si>
-  <si>
-    <t>Dryer Hours</t>
-  </si>
-  <si>
-    <t>Misc. Load</t>
-  </si>
-  <si>
-    <t>0.8 kW</t>
-  </si>
-  <si>
-    <t>Misc. Hours</t>
-  </si>
-  <si>
-    <t>3 h</t>
-  </si>
-  <si>
-    <t>Daily Energy</t>
-  </si>
-  <si>
-    <t>16.4 kWh/day</t>
-  </si>
-  <si>
-    <t>(1.5 kW * 4h) + (2.0 kW * 4h) + (0.8 kW * 3h)</t>
-  </si>
-  <si>
-    <t>48.0 kWh/day</t>
-  </si>
-  <si>
-    <t>(3.0 kW * 6h) + (4.0 kW * 6h) + (1.5 kW * 4h)</t>
-  </si>
-  <si>
-    <t>142.0 kWh/day</t>
-  </si>
-  <si>
-    <t>(7.5 kW * 8h) + (8.0 kW * 8h) + (3.0 kW * 6h)</t>
-  </si>
-  <si>
-    <t>---</t>
-  </si>
-  <si>
-    <t>PSH</t>
-  </si>
-  <si>
-    <t>5.5 h</t>
-  </si>
-  <si>
-    <t>Tracker Gain</t>
-  </si>
-  <si>
     <t>Effective PSH</t>
   </si>
   <si>
-    <t>6.6 h</t>
-  </si>
-  <si>
     <t>5.5 h * (1 + 0.20)</t>
   </si>
   <si>
     <t>System Derate</t>
   </si>
   <si>
-    <t>0.75</t>
-  </si>
-  <si>
     <t>Required PV (kWp)</t>
   </si>
   <si>
-    <t>3.3 kWp</t>
-  </si>
-  <si>
-    <t>16.4 kWh / (6.6 h * 0.75)</t>
-  </si>
-  <si>
-    <t>9.7 kWp</t>
-  </si>
-  <si>
-    <t>48.0 kWh / (6.6 h * 0.75)</t>
-  </si>
-  <si>
-    <t>28.7 kWp</t>
-  </si>
-  <si>
-    <t>142.0 kWh / (6.6 h * 0.75)</t>
+    <t>kwp</t>
   </si>
   <si>
     <t>Panel Wattage</t>
   </si>
   <si>
-    <t>400 W</t>
+    <t>w</t>
   </si>
   <si>
     <t>Number of Panels</t>
   </si>
   <si>
-    <t>8 panels</t>
-  </si>
-  <si>
-    <t>(3.3 kWp * 1000) / 400 W</t>
-  </si>
-  <si>
-    <t>24 panels</t>
-  </si>
-  <si>
-    <t>(9.7 kWp * 1000) / 400 W</t>
-  </si>
-  <si>
-    <t>72 panels</t>
-  </si>
-  <si>
-    <t>(28.7 kWp * 1000) / 400 W</t>
+    <t>19 panels</t>
   </si>
   <si>
     <t>Inverter Efficiency</t>
   </si>
   <si>
-    <t>90% (0.90)</t>
-  </si>
-  <si>
     <t>Battery DoD</t>
   </si>
   <si>
-    <t>80% (0.80)</t>
-  </si>
-  <si>
     <t>Required Battery (usable)</t>
   </si>
   <si>
-    <t>23 kWh</t>
-  </si>
-  <si>
-    <t>16.4 kWh / (0.90 * 0.80)</t>
-  </si>
-  <si>
-    <t>67 kWh</t>
-  </si>
-  <si>
-    <t>48.0 kWh / (0.90 * 0.80)</t>
-  </si>
-  <si>
-    <t>197 kWh</t>
-  </si>
-  <si>
-    <t>142.0 kWh / (0.90 * 0.80)</t>
-  </si>
-  <si>
     <t>Inverter Size</t>
   </si>
   <si>
-    <t>4.3 kW</t>
-  </si>
-  <si>
-    <t>Peak Load: 1.5 kW + 2.0 kW + 0.8 kW</t>
-  </si>
-  <si>
-    <t>8.5 kW</t>
-  </si>
-  <si>
-    <t>Peak Load: 3.0 kW + 4.0 kW + 1.5 kW</t>
-  </si>
-  <si>
-    <t>18.5 kW</t>
-  </si>
-  <si>
-    <t>Peak Load: 7.5 kW + 8.0 kW + 3.0 kW</t>
-  </si>
-  <si>
     <t>Scenario</t>
   </si>
   <si>
@@ -896,58 +767,7 @@
     <t>Inverter Size (kW, nominal)</t>
   </si>
   <si>
-    <t>Small farm (≈1 ha)</t>
-  </si>
-  <si>
-    <t>16.4</t>
-  </si>
-  <si>
-    <t>3.3</t>
-  </si>
-  <si>
-    <t>~8</t>
-  </si>
-  <si>
-    <t>~23</t>
-  </si>
-  <si>
-    <t>~4.3</t>
-  </si>
-  <si>
-    <t>Medium farm (≈5 ha)</t>
-  </si>
-  <si>
-    <t>48.0</t>
-  </si>
-  <si>
-    <t>9.7</t>
-  </si>
-  <si>
-    <t>~24</t>
-  </si>
-  <si>
-    <t>~67</t>
-  </si>
-  <si>
-    <t>~8.5</t>
-  </si>
-  <si>
-    <t>Large farm (≈20 ha)</t>
-  </si>
-  <si>
-    <t>142.0</t>
-  </si>
-  <si>
-    <t>28.7</t>
-  </si>
-  <si>
-    <t>~72</t>
-  </si>
-  <si>
-    <t>~197</t>
-  </si>
-  <si>
-    <t>~18.5</t>
+    <t>Small farm (≈2 ha)</t>
   </si>
   <si>
     <t>Project: Security system design for a 2-hectare mango drying farm.</t>
@@ -1784,7 +1604,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1887,6 +1707,18 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1899,18 +1731,22 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1999,28 +1835,24 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="42" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7432,102 +7264,102 @@
   </cols>
   <sheetData>
     <row r="4" spans="4:16" ht="18.75">
-      <c r="E4" s="76" t="s">
+      <c r="E4" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
-      <c r="M4" s="77"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="75"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="83"/>
+      <c r="K4" s="83"/>
+      <c r="L4" s="83"/>
+      <c r="M4" s="83"/>
+      <c r="N4" s="83"/>
+      <c r="O4" s="83"/>
+      <c r="P4" s="81"/>
     </row>
     <row r="5" spans="4:16" ht="15.75">
-      <c r="E5" s="72" t="s">
+      <c r="E5" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="68" t="s">
+      <c r="F5" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="68" t="s">
+      <c r="G5" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="68" t="s">
+      <c r="H5" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="68" t="s">
+      <c r="I5" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="J5" s="68" t="s">
+      <c r="J5" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="68" t="s">
+      <c r="K5" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="L5" s="68" t="s">
+      <c r="L5" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="M5" s="68" t="s">
+      <c r="M5" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="68" t="s">
+      <c r="N5" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="O5" s="66" t="s">
+      <c r="O5" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="P5" s="67" t="s">
+      <c r="P5" s="63" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="4:16" ht="15.75">
-      <c r="E6" s="73" t="s">
+      <c r="E6" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="67">
+      <c r="F6" s="63">
         <v>2</v>
       </c>
-      <c r="G6" s="67">
+      <c r="G6" s="63">
         <f>F6*100</f>
         <v>200</v>
       </c>
-      <c r="H6" s="67">
+      <c r="H6" s="63">
         <f>(G6*100)/1000</f>
         <v>20</v>
       </c>
-      <c r="I6" s="67">
+      <c r="I6" s="63">
         <f>H6*7</f>
         <v>140</v>
       </c>
-      <c r="J6" s="67">
+      <c r="J6" s="63">
         <f>H6/5</f>
         <v>4</v>
       </c>
-      <c r="K6" s="67">
+      <c r="K6" s="63">
         <f>(H6*100)/(5*60)</f>
         <v>6.666666666666667</v>
       </c>
-      <c r="L6" s="67">
+      <c r="L6" s="63">
         <f>0.0027*J6*35</f>
         <v>0.378</v>
       </c>
-      <c r="M6" s="67">
+      <c r="M6" s="63">
         <f>L6*0.45</f>
         <v>0.1701</v>
       </c>
-      <c r="N6" s="67">
+      <c r="N6" s="63">
         <f>M6</f>
         <v>0.1701</v>
       </c>
-      <c r="O6" s="67">
+      <c r="O6" s="63">
         <v>0.84799999999999998</v>
       </c>
-      <c r="P6" s="68">
+      <c r="P6" s="64">
         <v>4</v>
       </c>
     </row>
@@ -7537,99 +7369,99 @@
     </row>
     <row r="10" spans="4:16" ht="18.75">
       <c r="D10" s="34"/>
-      <c r="E10" s="74" t="s">
+      <c r="E10" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="75"/>
+      <c r="F10" s="81"/>
       <c r="G10" s="31"/>
       <c r="H10" s="31"/>
-      <c r="I10" s="78" t="s">
+      <c r="I10" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="79"/>
-      <c r="K10" s="79"/>
-      <c r="L10" s="79"/>
-      <c r="M10" s="79"/>
-      <c r="N10" s="79"/>
-      <c r="O10" s="80"/>
+      <c r="J10" s="85"/>
+      <c r="K10" s="85"/>
+      <c r="L10" s="85"/>
+      <c r="M10" s="85"/>
+      <c r="N10" s="85"/>
+      <c r="O10" s="86"/>
     </row>
     <row r="11" spans="4:16" ht="18.75">
       <c r="D11" s="34"/>
-      <c r="E11" s="67" t="s">
+      <c r="E11" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="67" t="s">
+      <c r="F11" s="63" t="s">
         <v>17</v>
       </c>
       <c r="G11" s="34"/>
       <c r="H11" s="34"/>
-      <c r="I11" s="69" t="s">
+      <c r="I11" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="J11" s="68" t="s">
+      <c r="J11" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="K11" s="68" t="s">
+      <c r="K11" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="L11" s="68" t="s">
+      <c r="L11" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="M11" s="68" t="s">
+      <c r="M11" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="N11" s="68" t="s">
+      <c r="N11" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="O11" s="70" t="s">
+      <c r="O11" s="66" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="4:16" ht="18.75">
       <c r="D12" s="34"/>
-      <c r="E12" s="67" t="s">
+      <c r="E12" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="F12" s="67">
+      <c r="F12" s="63">
         <v>120</v>
       </c>
       <c r="G12" s="34"/>
       <c r="H12" s="34"/>
-      <c r="I12" s="67">
+      <c r="I12" s="63">
         <f>F14</f>
         <v>1400</v>
       </c>
-      <c r="J12" s="67">
+      <c r="J12" s="63">
         <f>0.35*2000</f>
         <v>700</v>
       </c>
-      <c r="K12" s="67">
+      <c r="K12" s="63">
         <f>P6*F12</f>
         <v>480</v>
       </c>
-      <c r="L12" s="67">
+      <c r="L12" s="63">
         <f>F13</f>
         <v>800</v>
       </c>
-      <c r="M12" s="67">
+      <c r="M12" s="63">
         <f>F16</f>
         <v>300</v>
       </c>
-      <c r="N12" s="67">
+      <c r="N12" s="63">
         <f>F17</f>
         <v>2500</v>
       </c>
-      <c r="O12" s="71">
+      <c r="O12" s="67">
         <f>I12+J12+K12+L12+M12+N12</f>
         <v>6180</v>
       </c>
     </row>
     <row r="13" spans="4:16" ht="15.75">
       <c r="D13" s="34"/>
-      <c r="E13" s="67" t="s">
+      <c r="E13" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="67">
+      <c r="F13" s="63">
         <v>800</v>
       </c>
       <c r="G13" s="34"/>
@@ -7637,10 +7469,10 @@
     </row>
     <row r="14" spans="4:16" ht="15.75">
       <c r="D14" s="34"/>
-      <c r="E14" s="67" t="s">
+      <c r="E14" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="67">
+      <c r="F14" s="63">
         <v>1400</v>
       </c>
       <c r="G14" s="34"/>
@@ -7649,30 +7481,30 @@
     </row>
     <row r="15" spans="4:16" ht="15.75">
       <c r="D15" s="34"/>
-      <c r="E15" s="67" t="s">
+      <c r="E15" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="67" t="s">
+      <c r="F15" s="63" t="s">
         <v>29</v>
       </c>
       <c r="G15" s="34"/>
       <c r="H15" s="34"/>
     </row>
     <row r="16" spans="4:16" ht="15.75">
-      <c r="E16" s="67" t="s">
+      <c r="E16" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="67">
+      <c r="F16" s="63">
         <v>300</v>
       </c>
       <c r="G16" s="34"/>
       <c r="H16" s="34"/>
     </row>
     <row r="17" spans="5:8" ht="15.75">
-      <c r="E17" s="67" t="s">
+      <c r="E17" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="67">
+      <c r="F17" s="63">
         <v>2500</v>
       </c>
       <c r="G17" s="34"/>
@@ -7713,17 +7545,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="24">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
     </row>
     <row r="3" spans="1:16" ht="19.5">
       <c r="A3" s="2" t="s">
@@ -7753,16 +7585,16 @@
       <c r="I3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K3" s="83" t="s">
+      <c r="K3" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="L3" s="84"/>
-      <c r="M3" s="65"/>
+      <c r="L3" s="90"/>
+      <c r="M3" s="73"/>
       <c r="N3" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="O3" s="62"/>
-      <c r="P3" s="62"/>
+      <c r="O3" s="70"/>
+      <c r="P3" s="70"/>
     </row>
     <row r="4" spans="1:16" ht="21">
       <c r="A4" s="3">
@@ -7795,7 +7627,7 @@
       <c r="K4" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="L4" s="63" t="s">
+      <c r="L4" s="71" t="s">
         <v>45</v>
       </c>
       <c r="M4" s="7"/>
@@ -7803,7 +7635,7 @@
         <v>46</v>
       </c>
       <c r="O4" s="8"/>
-      <c r="P4" s="62"/>
+      <c r="P4" s="70"/>
     </row>
     <row r="5" spans="1:16" ht="21">
       <c r="A5" s="2">
@@ -7836,7 +7668,7 @@
       <c r="K5" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="L5" s="63" t="s">
+      <c r="L5" s="71" t="s">
         <v>48</v>
       </c>
       <c r="M5" s="7"/>
@@ -7844,7 +7676,7 @@
         <v>49</v>
       </c>
       <c r="O5" s="8"/>
-      <c r="P5" s="62"/>
+      <c r="P5" s="70"/>
     </row>
     <row r="6" spans="1:16" ht="21">
       <c r="A6" s="3">
@@ -7877,7 +7709,7 @@
       <c r="K6" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="L6" s="63" t="s">
+      <c r="L6" s="71" t="s">
         <v>51</v>
       </c>
       <c r="M6" s="9"/>
@@ -7885,7 +7717,7 @@
         <v>52</v>
       </c>
       <c r="O6" s="8"/>
-      <c r="P6" s="62"/>
+      <c r="P6" s="70"/>
     </row>
     <row r="7" spans="1:16" ht="21">
       <c r="A7" s="2">
@@ -7918,7 +7750,7 @@
       <c r="K7" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="63" t="s">
+      <c r="L7" s="71" t="s">
         <v>54</v>
       </c>
       <c r="M7" s="7"/>
@@ -7926,7 +7758,7 @@
         <v>55</v>
       </c>
       <c r="O7" s="8"/>
-      <c r="P7" s="62"/>
+      <c r="P7" s="70"/>
     </row>
     <row r="8" spans="1:16" ht="21">
       <c r="A8" s="3">
@@ -7959,7 +7791,7 @@
       <c r="K8" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="63" t="s">
+      <c r="L8" s="71" t="s">
         <v>57</v>
       </c>
       <c r="M8" s="7"/>
@@ -7967,7 +7799,7 @@
         <v>58</v>
       </c>
       <c r="O8" s="8"/>
-      <c r="P8" s="62"/>
+      <c r="P8" s="70"/>
     </row>
     <row r="9" spans="1:16" ht="21">
       <c r="A9" s="2">
@@ -7997,14 +7829,14 @@
       <c r="I9" s="1">
         <v>700000</v>
       </c>
-      <c r="K9" s="85" t="s">
+      <c r="K9" s="91" t="s">
         <v>59</v>
       </c>
-      <c r="L9" s="86"/>
+      <c r="L9" s="92"/>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
       <c r="O9" s="8"/>
-      <c r="P9" s="62"/>
+      <c r="P9" s="70"/>
     </row>
     <row r="10" spans="1:16" ht="21">
       <c r="A10" s="3">
@@ -8039,7 +7871,7 @@
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
       <c r="O10" s="8"/>
-      <c r="P10" s="62"/>
+      <c r="P10" s="70"/>
     </row>
     <row r="11" spans="1:16" ht="21">
       <c r="A11" s="2">
@@ -8069,14 +7901,14 @@
       <c r="I11" s="1">
         <v>535000</v>
       </c>
-      <c r="K11" s="87" t="s">
+      <c r="K11" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="88"/>
-      <c r="M11" s="88"/>
-      <c r="N11" s="88"/>
+      <c r="L11" s="94"/>
+      <c r="M11" s="94"/>
+      <c r="N11" s="94"/>
       <c r="O11" s="8"/>
-      <c r="P11" s="62"/>
+      <c r="P11" s="70"/>
     </row>
     <row r="12" spans="1:16" ht="21">
       <c r="A12" s="3">
@@ -8119,7 +7951,7 @@
         <v>64</v>
       </c>
       <c r="O12" s="8"/>
-      <c r="P12" s="62"/>
+      <c r="P12" s="70"/>
     </row>
     <row r="13" spans="1:16" ht="21">
       <c r="A13" s="2">
@@ -8149,20 +7981,20 @@
       <c r="I13" s="1">
         <v>425000</v>
       </c>
-      <c r="K13" s="63" t="s">
+      <c r="K13" s="71" t="s">
         <v>65</v>
       </c>
       <c r="L13" s="17">
         <v>3</v>
       </c>
-      <c r="M13" s="63" t="s">
+      <c r="M13" s="71" t="s">
         <v>66</v>
       </c>
-      <c r="N13" s="63" t="s">
+      <c r="N13" s="71" t="s">
         <v>67</v>
       </c>
       <c r="O13" s="8"/>
-      <c r="P13" s="62"/>
+      <c r="P13" s="70"/>
     </row>
     <row r="14" spans="1:16" ht="21">
       <c r="A14" s="3">
@@ -8192,20 +8024,20 @@
       <c r="I14" s="5">
         <v>370000</v>
       </c>
-      <c r="K14" s="63" t="s">
+      <c r="K14" s="71" t="s">
         <v>68</v>
       </c>
       <c r="L14" s="18">
         <v>5</v>
       </c>
-      <c r="M14" s="63" t="s">
+      <c r="M14" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="N14" s="63" t="s">
+      <c r="N14" s="71" t="s">
         <v>70</v>
       </c>
       <c r="O14" s="8"/>
-      <c r="P14" s="62"/>
+      <c r="P14" s="70"/>
     </row>
     <row r="15" spans="1:16" ht="21">
       <c r="A15" s="2">
@@ -8235,50 +8067,50 @@
       <c r="I15" s="1">
         <v>315000</v>
       </c>
-      <c r="K15" s="63" t="s">
+      <c r="K15" s="71" t="s">
         <v>71</v>
       </c>
       <c r="L15" s="17">
         <v>450</v>
       </c>
-      <c r="M15" s="63" t="s">
+      <c r="M15" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="N15" s="63" t="s">
+      <c r="N15" s="71" t="s">
         <v>73</v>
       </c>
       <c r="O15" s="8"/>
-      <c r="P15" s="62"/>
+      <c r="P15" s="70"/>
     </row>
     <row r="16" spans="1:16" ht="21">
-      <c r="K16" s="63" t="s">
+      <c r="K16" s="71" t="s">
         <v>74</v>
       </c>
-      <c r="L16" s="63">
+      <c r="L16" s="71">
         <v>75</v>
       </c>
-      <c r="M16" s="63" t="s">
+      <c r="M16" s="71" t="s">
         <v>75</v>
       </c>
-      <c r="N16" s="63" t="s">
+      <c r="N16" s="71" t="s">
         <v>76</v>
       </c>
       <c r="O16" s="8"/>
-      <c r="P16" s="62"/>
+      <c r="P16" s="70"/>
     </row>
     <row r="17" spans="1:9" ht="18.75">
-      <c r="A17" s="91" t="s">
+      <c r="A17" s="97" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="92"/>
-      <c r="C17" s="92"/>
-      <c r="D17" s="92"/>
-      <c r="F17" s="92" t="s">
+      <c r="B17" s="98"/>
+      <c r="C17" s="98"/>
+      <c r="D17" s="98"/>
+      <c r="F17" s="98" t="s">
         <v>78</v>
       </c>
-      <c r="G17" s="92"/>
-      <c r="H17" s="92"/>
-      <c r="I17" s="92"/>
+      <c r="G17" s="98"/>
+      <c r="H17" s="98"/>
+      <c r="I17" s="98"/>
     </row>
     <row r="18" spans="1:9" ht="36">
       <c r="A18" s="10" t="s">
@@ -8373,10 +8205,10 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="18.75">
-      <c r="A22" s="89" t="s">
+      <c r="A22" s="95" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="90"/>
+      <c r="B22" s="96"/>
       <c r="F22" s="12" t="s">
         <v>105</v>
       </c>
@@ -8502,34 +8334,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="59.25">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="100" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="94"/>
-      <c r="N1" s="94"/>
-      <c r="O1" s="94"/>
-      <c r="P1" s="94"/>
-      <c r="Q1" s="94"/>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
-      <c r="U1" s="94"/>
-      <c r="V1" s="94"/>
-      <c r="W1" s="94"/>
-      <c r="X1" s="94"/>
-      <c r="Y1" s="94"/>
-      <c r="Z1" s="94"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="100"/>
+      <c r="K1" s="100"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
+      <c r="N1" s="100"/>
+      <c r="O1" s="100"/>
+      <c r="P1" s="100"/>
+      <c r="Q1" s="100"/>
+      <c r="R1" s="100"/>
+      <c r="S1" s="100"/>
+      <c r="T1" s="100"/>
+      <c r="U1" s="100"/>
+      <c r="V1" s="100"/>
+      <c r="W1" s="100"/>
+      <c r="X1" s="100"/>
+      <c r="Y1" s="100"/>
+      <c r="Z1" s="100"/>
     </row>
     <row r="2" spans="1:26">
       <c r="A2" s="33"/>
@@ -8542,45 +8374,45 @@
       <c r="D4" s="34"/>
     </row>
     <row r="8" spans="1:26">
-      <c r="B8" s="95" t="s">
+      <c r="B8" s="101" t="s">
         <v>126</v>
       </c>
-      <c r="C8" s="95"/>
-      <c r="D8" s="96">
+      <c r="C8" s="101"/>
+      <c r="D8" s="102">
         <v>625</v>
       </c>
     </row>
     <row r="9" spans="1:26">
-      <c r="B9" s="95"/>
-      <c r="C9" s="95"/>
-      <c r="D9" s="97"/>
+      <c r="B9" s="101"/>
+      <c r="C9" s="101"/>
+      <c r="D9" s="103"/>
     </row>
     <row r="10" spans="1:26" ht="19.5">
-      <c r="B10" s="98" t="s">
+      <c r="B10" s="104" t="s">
         <v>127</v>
       </c>
-      <c r="C10" s="99"/>
+      <c r="C10" s="105"/>
       <c r="D10" s="58">
         <v>1600</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="18.75">
-      <c r="B14" s="91" t="s">
+      <c r="B14" s="97" t="s">
         <v>128</v>
       </c>
-      <c r="C14" s="91"/>
-      <c r="D14" s="91"/>
-      <c r="O14" s="100" t="s">
+      <c r="C14" s="97"/>
+      <c r="D14" s="97"/>
+      <c r="O14" s="106" t="s">
         <v>129</v>
       </c>
-      <c r="P14" s="100"/>
-      <c r="Q14" s="100"/>
-      <c r="R14" s="100"/>
-      <c r="S14" s="100"/>
-      <c r="T14" s="100"/>
-      <c r="U14" s="100"/>
-      <c r="V14" s="100"/>
-      <c r="W14" s="100"/>
+      <c r="P14" s="106"/>
+      <c r="Q14" s="106"/>
+      <c r="R14" s="106"/>
+      <c r="S14" s="106"/>
+      <c r="T14" s="106"/>
+      <c r="U14" s="106"/>
+      <c r="V14" s="106"/>
+      <c r="W14" s="106"/>
     </row>
     <row r="15" spans="1:26" ht="15.75">
       <c r="B15" s="46" t="s">
@@ -8592,11 +8424,11 @@
       <c r="D15" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="I15" s="101" t="s">
+      <c r="I15" s="107" t="s">
         <v>132</v>
       </c>
-      <c r="J15" s="101"/>
-      <c r="K15" s="101"/>
+      <c r="J15" s="107"/>
+      <c r="K15" s="107"/>
       <c r="O15" s="59" t="s">
         <v>133</v>
       </c>
@@ -8930,32 +8762,32 @@
       <c r="N31" s="35"/>
     </row>
     <row r="44" spans="3:26" ht="30">
-      <c r="C44" s="93" t="s">
+      <c r="C44" s="99" t="s">
         <v>178</v>
       </c>
-      <c r="D44" s="93"/>
-      <c r="E44" s="93"/>
-      <c r="F44" s="93"/>
-      <c r="G44" s="93"/>
-      <c r="H44" s="93"/>
-      <c r="I44" s="93"/>
-      <c r="J44" s="93"/>
-      <c r="K44" s="93"/>
-      <c r="L44" s="93"/>
-      <c r="M44" s="93"/>
-      <c r="N44" s="93"/>
-      <c r="O44" s="93"/>
-      <c r="P44" s="93"/>
-      <c r="Q44" s="93"/>
-      <c r="R44" s="93"/>
-      <c r="S44" s="93"/>
-      <c r="T44" s="93"/>
-      <c r="U44" s="93"/>
-      <c r="V44" s="93"/>
-      <c r="W44" s="93"/>
-      <c r="X44" s="93"/>
-      <c r="Y44" s="93"/>
-      <c r="Z44" s="93"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
+      <c r="F44" s="99"/>
+      <c r="G44" s="99"/>
+      <c r="H44" s="99"/>
+      <c r="I44" s="99"/>
+      <c r="J44" s="99"/>
+      <c r="K44" s="99"/>
+      <c r="L44" s="99"/>
+      <c r="M44" s="99"/>
+      <c r="N44" s="99"/>
+      <c r="O44" s="99"/>
+      <c r="P44" s="99"/>
+      <c r="Q44" s="99"/>
+      <c r="R44" s="99"/>
+      <c r="S44" s="99"/>
+      <c r="T44" s="99"/>
+      <c r="U44" s="99"/>
+      <c r="V44" s="99"/>
+      <c r="W44" s="99"/>
+      <c r="X44" s="99"/>
+      <c r="Y44" s="99"/>
+      <c r="Z44" s="99"/>
     </row>
     <row r="45" spans="3:26">
       <c r="C45" s="52" t="s">
@@ -9772,32 +9604,32 @@
       </c>
     </row>
     <row r="63" spans="3:26" ht="30">
-      <c r="C63" s="93" t="s">
+      <c r="C63" s="99" t="s">
         <v>203</v>
       </c>
-      <c r="D63" s="93"/>
-      <c r="E63" s="93"/>
-      <c r="F63" s="93"/>
-      <c r="G63" s="93"/>
-      <c r="H63" s="93"/>
-      <c r="I63" s="93"/>
-      <c r="J63" s="93"/>
-      <c r="K63" s="93"/>
-      <c r="L63" s="93"/>
-      <c r="M63" s="93"/>
-      <c r="N63" s="93"/>
-      <c r="O63" s="93"/>
-      <c r="P63" s="93"/>
-      <c r="Q63" s="93"/>
-      <c r="R63" s="93"/>
-      <c r="S63" s="93"/>
-      <c r="T63" s="93"/>
-      <c r="U63" s="93"/>
-      <c r="V63" s="93"/>
-      <c r="W63" s="93"/>
-      <c r="X63" s="93"/>
-      <c r="Y63" s="93"/>
-      <c r="Z63" s="93"/>
+      <c r="D63" s="99"/>
+      <c r="E63" s="99"/>
+      <c r="F63" s="99"/>
+      <c r="G63" s="99"/>
+      <c r="H63" s="99"/>
+      <c r="I63" s="99"/>
+      <c r="J63" s="99"/>
+      <c r="K63" s="99"/>
+      <c r="L63" s="99"/>
+      <c r="M63" s="99"/>
+      <c r="N63" s="99"/>
+      <c r="O63" s="99"/>
+      <c r="P63" s="99"/>
+      <c r="Q63" s="99"/>
+      <c r="R63" s="99"/>
+      <c r="S63" s="99"/>
+      <c r="T63" s="99"/>
+      <c r="U63" s="99"/>
+      <c r="V63" s="99"/>
+      <c r="W63" s="99"/>
+      <c r="X63" s="99"/>
+      <c r="Y63" s="99"/>
+      <c r="Z63" s="99"/>
     </row>
     <row r="64" spans="3:26">
       <c r="C64" s="52" t="s">
@@ -10614,32 +10446,32 @@
       </c>
     </row>
     <row r="81" spans="3:26" ht="30">
-      <c r="C81" s="93" t="s">
+      <c r="C81" s="99" t="s">
         <v>204</v>
       </c>
-      <c r="D81" s="93"/>
-      <c r="E81" s="93"/>
-      <c r="F81" s="93"/>
-      <c r="G81" s="93"/>
-      <c r="H81" s="93"/>
-      <c r="I81" s="93"/>
-      <c r="J81" s="93"/>
-      <c r="K81" s="93"/>
-      <c r="L81" s="93"/>
-      <c r="M81" s="93"/>
-      <c r="N81" s="93"/>
-      <c r="O81" s="93"/>
-      <c r="P81" s="93"/>
-      <c r="Q81" s="93"/>
-      <c r="R81" s="93"/>
-      <c r="S81" s="93"/>
-      <c r="T81" s="93"/>
-      <c r="U81" s="93"/>
-      <c r="V81" s="93"/>
-      <c r="W81" s="93"/>
-      <c r="X81" s="93"/>
-      <c r="Y81" s="93"/>
-      <c r="Z81" s="93"/>
+      <c r="D81" s="99"/>
+      <c r="E81" s="99"/>
+      <c r="F81" s="99"/>
+      <c r="G81" s="99"/>
+      <c r="H81" s="99"/>
+      <c r="I81" s="99"/>
+      <c r="J81" s="99"/>
+      <c r="K81" s="99"/>
+      <c r="L81" s="99"/>
+      <c r="M81" s="99"/>
+      <c r="N81" s="99"/>
+      <c r="O81" s="99"/>
+      <c r="P81" s="99"/>
+      <c r="Q81" s="99"/>
+      <c r="R81" s="99"/>
+      <c r="S81" s="99"/>
+      <c r="T81" s="99"/>
+      <c r="U81" s="99"/>
+      <c r="V81" s="99"/>
+      <c r="W81" s="99"/>
+      <c r="X81" s="99"/>
+      <c r="Y81" s="99"/>
+      <c r="Z81" s="99"/>
     </row>
     <row r="82" spans="3:26">
       <c r="C82" s="55" t="s">
@@ -11456,32 +11288,32 @@
       </c>
     </row>
     <row r="103" spans="3:26" ht="30">
-      <c r="C103" s="93" t="s">
+      <c r="C103" s="99" t="s">
         <v>205</v>
       </c>
-      <c r="D103" s="93"/>
-      <c r="E103" s="93"/>
-      <c r="F103" s="93"/>
-      <c r="G103" s="93"/>
-      <c r="H103" s="93"/>
-      <c r="I103" s="93"/>
-      <c r="J103" s="93"/>
-      <c r="K103" s="93"/>
-      <c r="L103" s="93"/>
-      <c r="M103" s="93"/>
-      <c r="N103" s="93"/>
-      <c r="O103" s="93"/>
-      <c r="P103" s="93"/>
-      <c r="Q103" s="93"/>
-      <c r="R103" s="93"/>
-      <c r="S103" s="93"/>
-      <c r="T103" s="93"/>
-      <c r="U103" s="93"/>
-      <c r="V103" s="93"/>
-      <c r="W103" s="93"/>
-      <c r="X103" s="93"/>
-      <c r="Y103" s="93"/>
-      <c r="Z103" s="93"/>
+      <c r="D103" s="99"/>
+      <c r="E103" s="99"/>
+      <c r="F103" s="99"/>
+      <c r="G103" s="99"/>
+      <c r="H103" s="99"/>
+      <c r="I103" s="99"/>
+      <c r="J103" s="99"/>
+      <c r="K103" s="99"/>
+      <c r="L103" s="99"/>
+      <c r="M103" s="99"/>
+      <c r="N103" s="99"/>
+      <c r="O103" s="99"/>
+      <c r="P103" s="99"/>
+      <c r="Q103" s="99"/>
+      <c r="R103" s="99"/>
+      <c r="S103" s="99"/>
+      <c r="T103" s="99"/>
+      <c r="U103" s="99"/>
+      <c r="V103" s="99"/>
+      <c r="W103" s="99"/>
+      <c r="X103" s="99"/>
+      <c r="Y103" s="99"/>
+      <c r="Z103" s="99"/>
     </row>
     <row r="104" spans="3:26">
       <c r="C104" s="55" t="s">
@@ -12340,653 +12172,385 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12">
-      <c r="C1" s="62" t="s">
+      <c r="C1" s="70" t="s">
         <v>206</v>
       </c>
-      <c r="G1" s="62" t="s">
+      <c r="G1" s="70"/>
+      <c r="K1" s="70"/>
+    </row>
+    <row r="3" spans="2:12">
+      <c r="B3" s="74" t="s">
         <v>207</v>
       </c>
-      <c r="K1" s="62" t="s">
+      <c r="C3" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" s="75" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="3" spans="2:12">
-      <c r="B3" s="106" t="s">
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
+      <c r="H3" s="112"/>
+      <c r="J3" s="112"/>
+      <c r="K3" s="112"/>
+      <c r="L3" s="112"/>
+    </row>
+    <row r="4" spans="2:12">
+      <c r="B4" s="76" t="s">
         <v>209</v>
       </c>
-      <c r="C3" s="107" t="s">
-        <v>130</v>
-      </c>
-      <c r="D3" s="107" t="s">
+      <c r="C4" s="115">
+        <v>1.5</v>
+      </c>
+      <c r="D4" s="115" t="s">
         <v>210</v>
       </c>
-      <c r="F3" s="106" t="s">
-        <v>209</v>
-      </c>
-      <c r="G3" s="107" t="s">
-        <v>130</v>
-      </c>
-      <c r="H3" s="107" t="s">
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="J4" s="112"/>
+      <c r="K4" s="112"/>
+      <c r="L4" s="112"/>
+    </row>
+    <row r="5" spans="2:12">
+      <c r="B5" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="C5" s="115">
+        <v>4</v>
+      </c>
+      <c r="D5" s="115" t="s">
+        <v>212</v>
+      </c>
+      <c r="F5" s="112"/>
+      <c r="G5" s="112"/>
+      <c r="H5" s="112"/>
+      <c r="J5" s="112"/>
+      <c r="K5" s="112"/>
+      <c r="L5" s="112"/>
+    </row>
+    <row r="6" spans="2:12">
+      <c r="B6" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="C6" s="115">
+        <v>2</v>
+      </c>
+      <c r="D6" s="115" t="s">
         <v>210</v>
       </c>
-      <c r="J3" s="106" t="s">
-        <v>209</v>
-      </c>
-      <c r="K3" s="107" t="s">
-        <v>130</v>
-      </c>
-      <c r="L3" s="107" t="s">
+      <c r="F6" s="112"/>
+      <c r="G6" s="112"/>
+      <c r="H6" s="112"/>
+      <c r="J6" s="112"/>
+      <c r="K6" s="112"/>
+      <c r="L6" s="112"/>
+    </row>
+    <row r="7" spans="2:12">
+      <c r="B7" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" s="115">
+        <v>4</v>
+      </c>
+      <c r="D7" s="115" t="s">
+        <v>212</v>
+      </c>
+      <c r="F7" s="112"/>
+      <c r="G7" s="112"/>
+      <c r="H7" s="112"/>
+      <c r="J7" s="112"/>
+      <c r="K7" s="112"/>
+      <c r="L7" s="112"/>
+    </row>
+    <row r="8" spans="2:12">
+      <c r="B8" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="C8" s="115">
+        <v>3</v>
+      </c>
+      <c r="D8" s="115" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="4" spans="2:12" ht="23.25">
-      <c r="B4" s="108" t="s">
-        <v>211</v>
-      </c>
-      <c r="C4" s="109" t="s">
+      <c r="F8" s="112"/>
+      <c r="G8" s="112"/>
+      <c r="H8" s="112"/>
+      <c r="J8" s="112"/>
+      <c r="K8" s="112"/>
+      <c r="L8" s="112"/>
+    </row>
+    <row r="9" spans="2:12">
+      <c r="B9" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="C9" s="115">
+        <v>5</v>
+      </c>
+      <c r="D9" s="115" t="s">
         <v>212</v>
       </c>
-      <c r="D4" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="F4" s="108" t="s">
-        <v>211</v>
-      </c>
-      <c r="G4" s="109" t="s">
-        <v>214</v>
-      </c>
-      <c r="H4" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="J4" s="108" t="s">
-        <v>211</v>
-      </c>
-      <c r="K4" s="109" t="s">
-        <v>215</v>
-      </c>
-      <c r="L4" s="109" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="23.25">
-      <c r="B5" s="108" t="s">
-        <v>216</v>
-      </c>
-      <c r="C5" s="109" t="s">
+      <c r="F9" s="112"/>
+      <c r="G9" s="112"/>
+      <c r="H9" s="112"/>
+      <c r="J9" s="112"/>
+      <c r="K9" s="112"/>
+      <c r="L9" s="112"/>
+    </row>
+    <row r="10" spans="2:12">
+      <c r="B10" s="76" t="s">
         <v>217</v>
       </c>
-      <c r="D5" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="F5" s="108" t="s">
-        <v>216</v>
-      </c>
-      <c r="G5" s="109" t="s">
+      <c r="C10" s="115">
+        <f>C4*C5+C5*C7+C8*C9</f>
+        <v>37</v>
+      </c>
+      <c r="D10" s="115" t="s">
         <v>218</v>
       </c>
-      <c r="H5" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="J5" s="108" t="s">
-        <v>216</v>
-      </c>
-      <c r="K5" s="109" t="s">
+      <c r="F10" s="112"/>
+      <c r="G10" s="112"/>
+      <c r="H10" s="112"/>
+      <c r="J10" s="112"/>
+      <c r="K10" s="112"/>
+      <c r="L10" s="112"/>
+    </row>
+    <row r="11" spans="2:12">
+      <c r="B11" s="78" t="s">
         <v>219</v>
       </c>
-      <c r="L5" s="109" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" ht="23.25">
-      <c r="B6" s="108" t="s">
+      <c r="C11" s="116" t="s">
+        <v>219</v>
+      </c>
+      <c r="D11" s="116" t="s">
+        <v>219</v>
+      </c>
+      <c r="F11" s="113"/>
+      <c r="G11" s="113"/>
+      <c r="H11" s="113"/>
+      <c r="J11" s="113"/>
+      <c r="K11" s="113"/>
+      <c r="L11" s="113"/>
+    </row>
+    <row r="12" spans="2:12">
+      <c r="B12" s="76" t="s">
         <v>220</v>
       </c>
-      <c r="C6" s="109" t="s">
+      <c r="C12" s="115">
+        <v>5.5</v>
+      </c>
+      <c r="D12" s="115" t="s">
+        <v>212</v>
+      </c>
+      <c r="F12" s="112"/>
+      <c r="G12" s="112"/>
+      <c r="H12" s="112"/>
+      <c r="J12" s="112"/>
+      <c r="K12" s="112"/>
+      <c r="L12" s="112"/>
+    </row>
+    <row r="13" spans="2:12">
+      <c r="B13" s="76" t="s">
         <v>221</v>
       </c>
-      <c r="D6" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="F6" s="108" t="s">
-        <v>220</v>
-      </c>
-      <c r="G6" s="109" t="s">
+      <c r="C13" s="117">
+        <v>0.2</v>
+      </c>
+      <c r="D13" s="115" t="s">
         <v>222</v>
       </c>
-      <c r="H6" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="J6" s="108" t="s">
-        <v>220</v>
-      </c>
-      <c r="K6" s="109" t="s">
+      <c r="F13" s="112"/>
+      <c r="G13" s="114"/>
+      <c r="H13" s="112"/>
+      <c r="J13" s="112"/>
+      <c r="K13" s="114"/>
+      <c r="L13" s="112"/>
+    </row>
+    <row r="14" spans="2:12">
+      <c r="B14" s="76" t="s">
         <v>223</v>
       </c>
-      <c r="L6" s="109" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="23.25">
-      <c r="B7" s="108" t="s">
+      <c r="C14" s="115">
+        <v>6.6</v>
+      </c>
+      <c r="D14" s="115" t="s">
         <v>224</v>
       </c>
-      <c r="C7" s="109" t="s">
-        <v>217</v>
-      </c>
-      <c r="D7" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="F7" s="108" t="s">
-        <v>224</v>
-      </c>
-      <c r="G7" s="109" t="s">
+      <c r="F14" s="112"/>
+      <c r="G14" s="112"/>
+      <c r="H14" s="112"/>
+      <c r="J14" s="112"/>
+      <c r="K14" s="112"/>
+      <c r="L14" s="112"/>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="B15" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="C15" s="115">
+        <v>0.75</v>
+      </c>
+      <c r="D15" s="115" t="s">
+        <v>222</v>
+      </c>
+      <c r="F15" s="112"/>
+      <c r="G15" s="112"/>
+      <c r="H15" s="112"/>
+      <c r="J15" s="112"/>
+      <c r="K15" s="112"/>
+      <c r="L15" s="112"/>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="B16" s="76" t="s">
+        <v>226</v>
+      </c>
+      <c r="C16" s="115">
+        <f>C10/(C14*C15)</f>
+        <v>7.4747474747474758</v>
+      </c>
+      <c r="D16" s="115" t="s">
+        <v>227</v>
+      </c>
+      <c r="F16" s="112"/>
+      <c r="G16" s="112"/>
+      <c r="H16" s="112"/>
+      <c r="J16" s="112"/>
+      <c r="K16" s="112"/>
+      <c r="L16" s="112"/>
+    </row>
+    <row r="17" spans="2:12">
+      <c r="B17" s="76" t="s">
+        <v>228</v>
+      </c>
+      <c r="C17" s="115">
+        <v>400</v>
+      </c>
+      <c r="D17" s="115" t="s">
+        <v>229</v>
+      </c>
+      <c r="F17" s="112"/>
+      <c r="G17" s="112"/>
+      <c r="H17" s="112"/>
+      <c r="J17" s="112"/>
+      <c r="K17" s="112"/>
+      <c r="L17" s="112"/>
+    </row>
+    <row r="18" spans="2:12">
+      <c r="B18" s="76" t="s">
+        <v>230</v>
+      </c>
+      <c r="C18" s="115">
+        <f>(C16*1000)/400</f>
+        <v>18.686868686868692</v>
+      </c>
+      <c r="D18" s="115" t="s">
+        <v>231</v>
+      </c>
+      <c r="F18" s="112"/>
+      <c r="G18" s="112"/>
+      <c r="H18" s="112"/>
+      <c r="J18" s="112"/>
+      <c r="K18" s="112"/>
+      <c r="L18" s="112"/>
+    </row>
+    <row r="19" spans="2:12">
+      <c r="B19" s="78" t="s">
+        <v>219</v>
+      </c>
+      <c r="C19" s="116" t="s">
+        <v>219</v>
+      </c>
+      <c r="D19" s="116" t="s">
+        <v>219</v>
+      </c>
+      <c r="F19" s="113"/>
+      <c r="G19" s="113"/>
+      <c r="H19" s="113"/>
+      <c r="J19" s="113"/>
+      <c r="K19" s="113"/>
+      <c r="L19" s="113"/>
+    </row>
+    <row r="20" spans="2:12">
+      <c r="B20" s="76" t="s">
+        <v>232</v>
+      </c>
+      <c r="C20" s="115">
+        <v>0.9</v>
+      </c>
+      <c r="D20" s="115"/>
+      <c r="F20" s="112"/>
+      <c r="G20" s="112"/>
+      <c r="H20" s="112"/>
+      <c r="J20" s="112"/>
+      <c r="K20" s="112"/>
+      <c r="L20" s="112"/>
+    </row>
+    <row r="21" spans="2:12">
+      <c r="B21" s="76" t="s">
+        <v>233</v>
+      </c>
+      <c r="C21" s="115">
+        <v>0.8</v>
+      </c>
+      <c r="D21" s="115"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="112"/>
+      <c r="H21" s="112"/>
+      <c r="J21" s="112"/>
+      <c r="K21" s="112"/>
+      <c r="L21" s="112"/>
+    </row>
+    <row r="22" spans="2:12" ht="23.25">
+      <c r="B22" s="76" t="s">
+        <v>234</v>
+      </c>
+      <c r="C22" s="115">
+        <f>C10/(C20*C21)</f>
+        <v>51.388888888888886</v>
+      </c>
+      <c r="D22" s="115" t="s">
         <v>218</v>
       </c>
-      <c r="H7" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="J7" s="108" t="s">
-        <v>224</v>
-      </c>
-      <c r="K7" s="109" t="s">
+      <c r="F22" s="112"/>
+      <c r="G22" s="112"/>
+      <c r="H22" s="112"/>
+      <c r="J22" s="112"/>
+      <c r="K22" s="112"/>
+      <c r="L22" s="112"/>
+    </row>
+    <row r="23" spans="2:12">
+      <c r="B23" s="78" t="s">
         <v>219</v>
       </c>
-      <c r="L7" s="109" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="23.25">
-      <c r="B8" s="108" t="s">
-        <v>225</v>
-      </c>
-      <c r="C8" s="109" t="s">
-        <v>226</v>
-      </c>
-      <c r="D8" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="F8" s="108" t="s">
-        <v>225</v>
-      </c>
-      <c r="G8" s="109" t="s">
-        <v>212</v>
-      </c>
-      <c r="H8" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="J8" s="108" t="s">
-        <v>225</v>
-      </c>
-      <c r="K8" s="109" t="s">
-        <v>214</v>
-      </c>
-      <c r="L8" s="109" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="23.25">
-      <c r="B9" s="108" t="s">
-        <v>227</v>
-      </c>
-      <c r="C9" s="109" t="s">
-        <v>228</v>
-      </c>
-      <c r="D9" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="F9" s="108" t="s">
-        <v>227</v>
-      </c>
-      <c r="G9" s="109" t="s">
-        <v>217</v>
-      </c>
-      <c r="H9" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="J9" s="108" t="s">
-        <v>227</v>
-      </c>
-      <c r="K9" s="109" t="s">
-        <v>218</v>
-      </c>
-      <c r="L9" s="109" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="23.25">
-      <c r="B10" s="108" t="s">
-        <v>229</v>
-      </c>
-      <c r="C10" s="109" t="s">
-        <v>230</v>
-      </c>
-      <c r="D10" s="109" t="s">
-        <v>231</v>
-      </c>
-      <c r="F10" s="108" t="s">
-        <v>229</v>
-      </c>
-      <c r="G10" s="109" t="s">
-        <v>232</v>
-      </c>
-      <c r="H10" s="109" t="s">
-        <v>233</v>
-      </c>
-      <c r="J10" s="108" t="s">
-        <v>229</v>
-      </c>
-      <c r="K10" s="109" t="s">
-        <v>234</v>
-      </c>
-      <c r="L10" s="109" t="s">
+      <c r="C23" s="116" t="s">
+        <v>219</v>
+      </c>
+      <c r="D23" s="116" t="s">
+        <v>219</v>
+      </c>
+      <c r="F23" s="113"/>
+      <c r="G23" s="113"/>
+      <c r="H23" s="113"/>
+      <c r="J23" s="113"/>
+      <c r="K23" s="113"/>
+      <c r="L23" s="113"/>
+    </row>
+    <row r="24" spans="2:12">
+      <c r="B24" s="76" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="11" spans="2:12">
-      <c r="B11" s="110" t="s">
-        <v>236</v>
-      </c>
-      <c r="C11" s="111" t="s">
-        <v>236</v>
-      </c>
-      <c r="D11" s="111" t="s">
-        <v>236</v>
-      </c>
-      <c r="F11" s="110" t="s">
-        <v>236</v>
-      </c>
-      <c r="G11" s="111" t="s">
-        <v>236</v>
-      </c>
-      <c r="H11" s="111" t="s">
-        <v>236</v>
-      </c>
-      <c r="J11" s="110" t="s">
-        <v>236</v>
-      </c>
-      <c r="K11" s="111" t="s">
-        <v>236</v>
-      </c>
-      <c r="L11" s="111" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12">
-      <c r="B12" s="108" t="s">
-        <v>237</v>
-      </c>
-      <c r="C12" s="109" t="s">
-        <v>238</v>
-      </c>
-      <c r="D12" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="F12" s="108" t="s">
-        <v>237</v>
-      </c>
-      <c r="G12" s="109" t="s">
-        <v>238</v>
-      </c>
-      <c r="H12" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="J12" s="108" t="s">
-        <v>237</v>
-      </c>
-      <c r="K12" s="109" t="s">
-        <v>238</v>
-      </c>
-      <c r="L12" s="109" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="23.25">
-      <c r="B13" s="108" t="s">
-        <v>239</v>
-      </c>
-      <c r="C13" s="112">
-        <v>0.2</v>
-      </c>
-      <c r="D13" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="F13" s="108" t="s">
-        <v>239</v>
-      </c>
-      <c r="G13" s="112">
-        <v>0.2</v>
-      </c>
-      <c r="H13" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="J13" s="108" t="s">
-        <v>239</v>
-      </c>
-      <c r="K13" s="112">
-        <v>0.2</v>
-      </c>
-      <c r="L13" s="109" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="23.25">
-      <c r="B14" s="108" t="s">
-        <v>240</v>
-      </c>
-      <c r="C14" s="109" t="s">
-        <v>241</v>
-      </c>
-      <c r="D14" s="109" t="s">
-        <v>242</v>
-      </c>
-      <c r="F14" s="108" t="s">
-        <v>240</v>
-      </c>
-      <c r="G14" s="109" t="s">
-        <v>241</v>
-      </c>
-      <c r="H14" s="109" t="s">
-        <v>242</v>
-      </c>
-      <c r="J14" s="108" t="s">
-        <v>240</v>
-      </c>
-      <c r="K14" s="109" t="s">
-        <v>241</v>
-      </c>
-      <c r="L14" s="109" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="23.25">
-      <c r="B15" s="108" t="s">
-        <v>243</v>
-      </c>
-      <c r="C15" s="109" t="s">
-        <v>244</v>
-      </c>
-      <c r="D15" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="F15" s="108" t="s">
-        <v>243</v>
-      </c>
-      <c r="G15" s="109" t="s">
-        <v>244</v>
-      </c>
-      <c r="H15" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="J15" s="108" t="s">
-        <v>243</v>
-      </c>
-      <c r="K15" s="109" t="s">
-        <v>244</v>
-      </c>
-      <c r="L15" s="109" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="23.25">
-      <c r="B16" s="108" t="s">
-        <v>245</v>
-      </c>
-      <c r="C16" s="109" t="s">
-        <v>246</v>
-      </c>
-      <c r="D16" s="109" t="s">
-        <v>247</v>
-      </c>
-      <c r="F16" s="108" t="s">
-        <v>245</v>
-      </c>
-      <c r="G16" s="109" t="s">
-        <v>248</v>
-      </c>
-      <c r="H16" s="109" t="s">
-        <v>249</v>
-      </c>
-      <c r="J16" s="108" t="s">
-        <v>245</v>
-      </c>
-      <c r="K16" s="109" t="s">
-        <v>250</v>
-      </c>
-      <c r="L16" s="109" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" ht="23.25">
-      <c r="B17" s="108" t="s">
-        <v>252</v>
-      </c>
-      <c r="C17" s="109" t="s">
-        <v>253</v>
-      </c>
-      <c r="D17" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="F17" s="108" t="s">
-        <v>252</v>
-      </c>
-      <c r="G17" s="109" t="s">
-        <v>253</v>
-      </c>
-      <c r="H17" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="J17" s="108" t="s">
-        <v>252</v>
-      </c>
-      <c r="K17" s="109" t="s">
-        <v>253</v>
-      </c>
-      <c r="L17" s="109" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" ht="23.25">
-      <c r="B18" s="108" t="s">
-        <v>254</v>
-      </c>
-      <c r="C18" s="109" t="s">
-        <v>255</v>
-      </c>
-      <c r="D18" s="109" t="s">
-        <v>256</v>
-      </c>
-      <c r="F18" s="108" t="s">
-        <v>254</v>
-      </c>
-      <c r="G18" s="109" t="s">
-        <v>257</v>
-      </c>
-      <c r="H18" s="109" t="s">
-        <v>258</v>
-      </c>
-      <c r="J18" s="108" t="s">
-        <v>254</v>
-      </c>
-      <c r="K18" s="109" t="s">
-        <v>259</v>
-      </c>
-      <c r="L18" s="109" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12">
-      <c r="B19" s="110" t="s">
-        <v>236</v>
-      </c>
-      <c r="C19" s="111" t="s">
-        <v>236</v>
-      </c>
-      <c r="D19" s="111" t="s">
-        <v>236</v>
-      </c>
-      <c r="F19" s="110" t="s">
-        <v>236</v>
-      </c>
-      <c r="G19" s="111" t="s">
-        <v>236</v>
-      </c>
-      <c r="H19" s="111" t="s">
-        <v>236</v>
-      </c>
-      <c r="J19" s="110" t="s">
-        <v>236</v>
-      </c>
-      <c r="K19" s="111" t="s">
-        <v>236</v>
-      </c>
-      <c r="L19" s="111" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" ht="23.25">
-      <c r="B20" s="108" t="s">
-        <v>261</v>
-      </c>
-      <c r="C20" s="109" t="s">
-        <v>262</v>
-      </c>
-      <c r="D20" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="F20" s="108" t="s">
-        <v>261</v>
-      </c>
-      <c r="G20" s="109" t="s">
-        <v>262</v>
-      </c>
-      <c r="H20" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="J20" s="108" t="s">
-        <v>261</v>
-      </c>
-      <c r="K20" s="109" t="s">
-        <v>262</v>
-      </c>
-      <c r="L20" s="109" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" ht="23.25">
-      <c r="B21" s="108" t="s">
-        <v>263</v>
-      </c>
-      <c r="C21" s="109" t="s">
-        <v>264</v>
-      </c>
-      <c r="D21" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="F21" s="108" t="s">
-        <v>263</v>
-      </c>
-      <c r="G21" s="109" t="s">
-        <v>264</v>
-      </c>
-      <c r="H21" s="109" t="s">
-        <v>213</v>
-      </c>
-      <c r="J21" s="108" t="s">
-        <v>263</v>
-      </c>
-      <c r="K21" s="109" t="s">
-        <v>264</v>
-      </c>
-      <c r="L21" s="109" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" ht="35.25">
-      <c r="B22" s="108" t="s">
-        <v>265</v>
-      </c>
-      <c r="C22" s="109" t="s">
-        <v>266</v>
-      </c>
-      <c r="D22" s="109" t="s">
-        <v>267</v>
-      </c>
-      <c r="F22" s="108" t="s">
-        <v>265</v>
-      </c>
-      <c r="G22" s="109" t="s">
-        <v>268</v>
-      </c>
-      <c r="H22" s="109" t="s">
-        <v>269</v>
-      </c>
-      <c r="J22" s="108" t="s">
-        <v>265</v>
-      </c>
-      <c r="K22" s="109" t="s">
-        <v>270</v>
-      </c>
-      <c r="L22" s="109" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12">
-      <c r="B23" s="110" t="s">
-        <v>236</v>
-      </c>
-      <c r="C23" s="111" t="s">
-        <v>236</v>
-      </c>
-      <c r="D23" s="111" t="s">
-        <v>236</v>
-      </c>
-      <c r="F23" s="110" t="s">
-        <v>236</v>
-      </c>
-      <c r="G23" s="111" t="s">
-        <v>236</v>
-      </c>
-      <c r="H23" s="111" t="s">
-        <v>236</v>
-      </c>
-      <c r="J23" s="110" t="s">
-        <v>236</v>
-      </c>
-      <c r="K23" s="111" t="s">
-        <v>236</v>
-      </c>
-      <c r="L23" s="111" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" ht="23.25">
-      <c r="B24" s="108" t="s">
-        <v>272</v>
-      </c>
-      <c r="C24" s="109" t="s">
-        <v>273</v>
-      </c>
-      <c r="D24" s="109" t="s">
-        <v>274</v>
-      </c>
-      <c r="F24" s="108" t="s">
-        <v>272</v>
-      </c>
-      <c r="G24" s="109" t="s">
-        <v>275</v>
-      </c>
-      <c r="H24" s="109" t="s">
-        <v>276</v>
-      </c>
-      <c r="J24" s="108" t="s">
-        <v>272</v>
-      </c>
-      <c r="K24" s="109" t="s">
-        <v>277</v>
-      </c>
-      <c r="L24" s="109" t="s">
-        <v>278</v>
-      </c>
+      <c r="C24" s="115">
+        <v>6.5</v>
+      </c>
+      <c r="D24" s="115" t="s">
+        <v>210</v>
+      </c>
+      <c r="F24" s="112"/>
+      <c r="G24" s="112"/>
+      <c r="H24" s="112"/>
+      <c r="J24" s="112"/>
+      <c r="K24" s="112"/>
+      <c r="L24" s="112"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12995,7 +12559,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549D1EB9-DCF8-4E0D-A2D2-EFBE00CED3CD}">
-  <dimension ref="B4:G7"/>
+  <dimension ref="B4:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="21.28515625" customWidth="1"/>
@@ -13007,83 +12571,43 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:7" ht="23.25">
-      <c r="B4" s="106" t="s">
-        <v>279</v>
-      </c>
-      <c r="C4" s="107" t="s">
-        <v>280</v>
-      </c>
-      <c r="D4" s="107" t="s">
-        <v>281</v>
-      </c>
-      <c r="E4" s="107" t="s">
-        <v>282</v>
-      </c>
-      <c r="F4" s="107" t="s">
-        <v>283</v>
-      </c>
-      <c r="G4" s="113" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="35.25">
-      <c r="B5" s="108" t="s">
-        <v>285</v>
-      </c>
-      <c r="C5" s="109" t="s">
-        <v>286</v>
-      </c>
-      <c r="D5" s="109" t="s">
-        <v>287</v>
-      </c>
-      <c r="E5" s="109" t="s">
-        <v>288</v>
-      </c>
-      <c r="F5" s="109" t="s">
-        <v>289</v>
-      </c>
-      <c r="G5" s="109" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="35.25">
-      <c r="B6" s="108" t="s">
-        <v>291</v>
-      </c>
-      <c r="C6" s="109" t="s">
-        <v>292</v>
-      </c>
-      <c r="D6" s="109" t="s">
-        <v>293</v>
-      </c>
-      <c r="E6" s="109" t="s">
-        <v>294</v>
-      </c>
-      <c r="F6" s="109" t="s">
-        <v>295</v>
-      </c>
-      <c r="G6" s="109" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" ht="35.25">
-      <c r="B7" s="108" t="s">
-        <v>297</v>
-      </c>
-      <c r="C7" s="109" t="s">
-        <v>298</v>
-      </c>
-      <c r="D7" s="109" t="s">
-        <v>299</v>
-      </c>
-      <c r="E7" s="109" t="s">
-        <v>300</v>
-      </c>
-      <c r="F7" s="109" t="s">
-        <v>301</v>
-      </c>
-      <c r="G7" s="109" t="s">
-        <v>302</v>
+      <c r="B4" s="74" t="s">
+        <v>236</v>
+      </c>
+      <c r="C4" s="75" t="s">
+        <v>237</v>
+      </c>
+      <c r="D4" s="75" t="s">
+        <v>238</v>
+      </c>
+      <c r="E4" s="75" t="s">
+        <v>239</v>
+      </c>
+      <c r="F4" s="75" t="s">
+        <v>240</v>
+      </c>
+      <c r="G4" s="79" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="14.25">
+      <c r="B5" s="76" t="s">
+        <v>242</v>
+      </c>
+      <c r="C5" s="77">
+        <v>37</v>
+      </c>
+      <c r="D5" s="77">
+        <v>7.5</v>
+      </c>
+      <c r="E5" s="77">
+        <v>19</v>
+      </c>
+      <c r="F5" s="77">
+        <v>52</v>
+      </c>
+      <c r="G5" s="77">
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -13117,63 +12641,63 @@
       <c r="F5" s="22"/>
     </row>
     <row r="6" spans="3:6">
-      <c r="C6" s="102" t="s">
-        <v>303</v>
-      </c>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
+      <c r="C6" s="108" t="s">
+        <v>243</v>
+      </c>
+      <c r="D6" s="108"/>
+      <c r="E6" s="108"/>
+      <c r="F6" s="108"/>
     </row>
     <row r="7" spans="3:6">
-      <c r="C7" s="102" t="s">
-        <v>304</v>
-      </c>
-      <c r="D7" s="102"/>
-      <c r="E7" s="102"/>
-      <c r="F7" s="102"/>
+      <c r="C7" s="108" t="s">
+        <v>244</v>
+      </c>
+      <c r="D7" s="108"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="108"/>
     </row>
     <row r="8" spans="3:6">
-      <c r="C8" s="103" t="s">
-        <v>305</v>
-      </c>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
-      <c r="F8" s="103"/>
+      <c r="C8" s="109" t="s">
+        <v>245</v>
+      </c>
+      <c r="D8" s="109"/>
+      <c r="E8" s="109"/>
+      <c r="F8" s="109"/>
     </row>
     <row r="9" spans="3:6">
-      <c r="C9" s="104" t="s">
-        <v>305</v>
-      </c>
-      <c r="D9" s="105"/>
-      <c r="E9" s="105"/>
-      <c r="F9" s="105"/>
+      <c r="C9" s="110" t="s">
+        <v>245</v>
+      </c>
+      <c r="D9" s="111"/>
+      <c r="E9" s="111"/>
+      <c r="F9" s="111"/>
     </row>
     <row r="10" spans="3:6">
-      <c r="C10" s="64"/>
-      <c r="D10" s="65"/>
-      <c r="E10" s="65"/>
-      <c r="F10" s="65"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
     </row>
     <row r="11" spans="3:6" ht="15.75">
       <c r="C11" s="23" t="s">
-        <v>306</v>
+        <v>246</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>308</v>
+        <v>248</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>309</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" spans="3:6" ht="15.75">
       <c r="C12" s="24" t="s">
-        <v>310</v>
+        <v>250</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>311</v>
+        <v>251</v>
       </c>
       <c r="E12" s="26">
         <v>9</v>
@@ -13184,7 +12708,7 @@
     </row>
     <row r="13" spans="3:6" ht="15.75">
       <c r="C13" s="27" t="s">
-        <v>312</v>
+        <v>252</v>
       </c>
       <c r="D13" s="27">
         <v>12</v>
@@ -13198,7 +12722,7 @@
     </row>
     <row r="14" spans="3:6" ht="15.75">
       <c r="C14" s="25" t="s">
-        <v>313</v>
+        <v>253</v>
       </c>
       <c r="D14" s="25">
         <v>2</v>
@@ -13212,7 +12736,7 @@
     </row>
     <row r="15" spans="3:6" ht="15.75">
       <c r="C15" s="27" t="s">
-        <v>314</v>
+        <v>254</v>
       </c>
       <c r="D15" s="27">
         <v>8</v>
@@ -13226,7 +12750,7 @@
     </row>
     <row r="16" spans="3:6" ht="15.75">
       <c r="C16" s="25" t="s">
-        <v>315</v>
+        <v>255</v>
       </c>
       <c r="D16" s="25">
         <v>2</v>
@@ -13240,7 +12764,7 @@
     </row>
     <row r="17" spans="3:6" ht="15.75">
       <c r="C17" s="27" t="s">
-        <v>316</v>
+        <v>256</v>
       </c>
       <c r="D17" s="27">
         <v>1</v>
@@ -13254,13 +12778,13 @@
     </row>
     <row r="18" spans="3:6" ht="15.75">
       <c r="C18" s="24" t="s">
-        <v>317</v>
+        <v>257</v>
       </c>
       <c r="D18" s="29" t="s">
-        <v>318</v>
+        <v>258</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>318</v>
+        <v>258</v>
       </c>
       <c r="F18" s="30">
         <v>10700</v>
